--- a/tiktok-analytics/data/20260601/订单收入大表_20260601_20260601_145441.xlsx
+++ b/tiktok-analytics/data/20260601/订单收入大表_20260601_20260601_145441.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F8A479-7384-9046-BD72-CB463C37FC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="3560" windowWidth="35040" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1660" yWindow="1920" windowWidth="35040" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>

--- a/tiktok-analytics/data/20260601/订单收入大表_20260601_20260601_145441.xlsx
+++ b/tiktok-analytics/data/20260601/订单收入大表_20260601_20260601_145441.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jianing/Ning's Git/tiktok-analytics/data/20260601/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F8A479-7384-9046-BD72-CB463C37FC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D39A7C-4184-0D43-9407-791303AF63AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1660" yWindow="1920" windowWidth="35040" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7440" yWindow="-32020" windowWidth="35040" windowHeight="21440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="样品订单" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Normal订单!$Q$1:$Q$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Normal订单!$D$1:$D$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -14414,6 +14414,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -14539,7 +14540,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" hidden="1">
       <c r="A3" s="2" t="s">
         <v>86</v>
       </c>
@@ -14595,7 +14596,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" hidden="1">
       <c r="A4" s="2" t="s">
         <v>89</v>
       </c>
@@ -14651,7 +14652,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17">
+    <row r="5" spans="1:18" ht="17" hidden="1">
       <c r="A5" s="2" t="s">
         <v>91</v>
       </c>
@@ -14707,7 +14708,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" hidden="1">
       <c r="A6" s="2" t="s">
         <v>93</v>
       </c>
@@ -14763,7 +14764,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" hidden="1">
       <c r="A7" s="2" t="s">
         <v>95</v>
       </c>
@@ -14819,7 +14820,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" hidden="1">
       <c r="A8" s="2" t="s">
         <v>95</v>
       </c>
@@ -14875,7 +14876,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" hidden="1">
       <c r="A9" s="2" t="s">
         <v>97</v>
       </c>
@@ -14931,7 +14932,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" hidden="1">
       <c r="A10" s="2" t="s">
         <v>97</v>
       </c>
@@ -15043,7 +15044,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" hidden="1">
       <c r="A12" s="2" t="s">
         <v>102</v>
       </c>
@@ -15211,7 +15212,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" hidden="1">
       <c r="A15" s="2" t="s">
         <v>108</v>
       </c>
@@ -15267,7 +15268,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" hidden="1">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -15379,7 +15380,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" hidden="1">
       <c r="A18" s="2" t="s">
         <v>115</v>
       </c>
@@ -15435,7 +15436,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" hidden="1">
       <c r="A19" s="2" t="s">
         <v>117</v>
       </c>
@@ -15547,7 +15548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" hidden="1">
       <c r="A21" s="2" t="s">
         <v>121</v>
       </c>
@@ -15603,7 +15604,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" hidden="1">
       <c r="A22" s="2" t="s">
         <v>121</v>
       </c>
@@ -15659,7 +15660,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" hidden="1">
       <c r="A23" s="2" t="s">
         <v>123</v>
       </c>
@@ -15715,7 +15716,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" hidden="1">
       <c r="A24" s="2" t="s">
         <v>125</v>
       </c>
@@ -15771,7 +15772,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" hidden="1">
       <c r="A25" s="2" t="s">
         <v>125</v>
       </c>
@@ -15827,7 +15828,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" hidden="1">
       <c r="A26" s="2" t="s">
         <v>127</v>
       </c>
@@ -15883,7 +15884,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" hidden="1">
       <c r="A27" s="2" t="s">
         <v>129</v>
       </c>
@@ -15939,7 +15940,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" hidden="1">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -16051,7 +16052,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" hidden="1">
       <c r="A30" s="2" t="s">
         <v>133</v>
       </c>
@@ -16107,7 +16108,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" hidden="1">
       <c r="A31" s="2" t="s">
         <v>135</v>
       </c>
@@ -16163,7 +16164,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" hidden="1">
       <c r="A32" s="2" t="s">
         <v>137</v>
       </c>
@@ -16219,7 +16220,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" hidden="1">
       <c r="A33" s="2" t="s">
         <v>139</v>
       </c>
@@ -16275,7 +16276,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" hidden="1">
       <c r="A34" s="2" t="s">
         <v>141</v>
       </c>
@@ -16331,7 +16332,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" hidden="1">
       <c r="A35" s="2" t="s">
         <v>143</v>
       </c>
@@ -16443,7 +16444,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:18" hidden="1">
       <c r="A37" s="2" t="s">
         <v>147</v>
       </c>
@@ -16555,7 +16556,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:18" hidden="1">
       <c r="A39" s="2" t="s">
         <v>151</v>
       </c>
@@ -16611,7 +16612,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" hidden="1">
       <c r="A40" s="2" t="s">
         <v>153</v>
       </c>
@@ -16667,7 +16668,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" hidden="1">
       <c r="A41" s="2" t="s">
         <v>155</v>
       </c>
@@ -16723,7 +16724,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:18" hidden="1">
       <c r="A42" s="2" t="s">
         <v>157</v>
       </c>
@@ -16947,7 +16948,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:18" hidden="1">
       <c r="A46" s="2" t="s">
         <v>165</v>
       </c>
@@ -17003,7 +17004,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:18" hidden="1">
       <c r="A47" s="2" t="s">
         <v>167</v>
       </c>
@@ -17115,7 +17116,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:18" hidden="1">
       <c r="A49" s="2" t="s">
         <v>171</v>
       </c>
@@ -17171,7 +17172,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:18" hidden="1">
       <c r="A50" s="2" t="s">
         <v>171</v>
       </c>
@@ -17395,7 +17396,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:18" hidden="1">
       <c r="A54" s="2" t="s">
         <v>180</v>
       </c>
@@ -17451,7 +17452,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:18" hidden="1">
       <c r="A55" s="2" t="s">
         <v>182</v>
       </c>
@@ -17563,7 +17564,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:18" hidden="1">
       <c r="A57" s="2" t="s">
         <v>186</v>
       </c>
@@ -17619,7 +17620,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
+    <row r="58" spans="1:18" hidden="1">
       <c r="A58" s="2" t="s">
         <v>186</v>
       </c>
@@ -17731,7 +17732,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:18" hidden="1">
       <c r="A60" s="2" t="s">
         <v>190</v>
       </c>
@@ -17787,7 +17788,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:18" hidden="1">
       <c r="A61" s="2" t="s">
         <v>192</v>
       </c>
@@ -17955,7 +17956,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" hidden="1">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -18011,7 +18012,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:18">
+    <row r="65" spans="1:18" hidden="1">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -18067,7 +18068,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
+    <row r="66" spans="1:18" hidden="1">
       <c r="A66" s="2" t="s">
         <v>200</v>
       </c>
@@ -18123,7 +18124,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:18" hidden="1">
       <c r="A67" s="2" t="s">
         <v>202</v>
       </c>
@@ -18179,7 +18180,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
+    <row r="68" spans="1:18" hidden="1">
       <c r="A68" s="2" t="s">
         <v>204</v>
       </c>
@@ -18235,7 +18236,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:18">
+    <row r="69" spans="1:18" hidden="1">
       <c r="A69" s="2" t="s">
         <v>204</v>
       </c>
@@ -18347,7 +18348,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="71" spans="1:18">
+    <row r="71" spans="1:18" hidden="1">
       <c r="A71" s="2" t="s">
         <v>208</v>
       </c>
@@ -18403,7 +18404,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:18" hidden="1">
       <c r="A72" s="2" t="s">
         <v>210</v>
       </c>
@@ -18459,7 +18460,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:18" hidden="1">
       <c r="A73" s="2" t="s">
         <v>210</v>
       </c>
@@ -18627,7 +18628,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:18" hidden="1">
       <c r="A76" s="2" t="s">
         <v>216</v>
       </c>
@@ -18683,7 +18684,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:18" hidden="1">
       <c r="A77" s="2" t="s">
         <v>216</v>
       </c>
@@ -18739,7 +18740,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:18" hidden="1">
       <c r="A78" s="2" t="s">
         <v>218</v>
       </c>
@@ -18795,7 +18796,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:18" hidden="1">
       <c r="A79" s="2" t="s">
         <v>220</v>
       </c>
@@ -18851,7 +18852,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:18" hidden="1">
       <c r="A80" s="2" t="s">
         <v>220</v>
       </c>
@@ -18907,7 +18908,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:18" hidden="1">
       <c r="A81" s="2" t="s">
         <v>222</v>
       </c>
@@ -18963,7 +18964,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:18" hidden="1">
       <c r="A82" s="2" t="s">
         <v>222</v>
       </c>
@@ -19075,7 +19076,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:18" hidden="1">
       <c r="A84" s="2" t="s">
         <v>226</v>
       </c>
@@ -19131,7 +19132,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" hidden="1">
       <c r="A85" s="2" t="s">
         <v>226</v>
       </c>
@@ -19299,7 +19300,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:18" hidden="1">
       <c r="A88" s="2" t="s">
         <v>232</v>
       </c>
@@ -19355,7 +19356,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" hidden="1">
       <c r="A89" s="2" t="s">
         <v>234</v>
       </c>
@@ -19467,7 +19468,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" hidden="1">
       <c r="A91" s="2" t="s">
         <v>238</v>
       </c>
@@ -19523,7 +19524,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:18" hidden="1">
       <c r="A92" s="2" t="s">
         <v>240</v>
       </c>
@@ -19635,7 +19636,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:18" hidden="1">
       <c r="A94" s="2" t="s">
         <v>244</v>
       </c>
@@ -19691,7 +19692,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:18" hidden="1">
       <c r="A95" s="2" t="s">
         <v>246</v>
       </c>
@@ -19747,7 +19748,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:18" hidden="1">
       <c r="A96" s="2" t="s">
         <v>248</v>
       </c>
@@ -19803,7 +19804,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:18" hidden="1">
       <c r="A97" s="2" t="s">
         <v>250</v>
       </c>
@@ -19859,7 +19860,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" hidden="1">
       <c r="A98" s="2" t="s">
         <v>252</v>
       </c>
@@ -19915,7 +19916,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:18" hidden="1">
       <c r="A99" s="2" t="s">
         <v>254</v>
       </c>
@@ -19971,7 +19972,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:18" hidden="1">
       <c r="A100" s="2" t="s">
         <v>254</v>
       </c>
@@ -20027,7 +20028,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:18" hidden="1">
       <c r="A101" s="2" t="s">
         <v>256</v>
       </c>
@@ -20083,7 +20084,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:18" hidden="1">
       <c r="A102" s="2" t="s">
         <v>256</v>
       </c>
@@ -20139,7 +20140,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:18" hidden="1">
       <c r="A103" s="2" t="s">
         <v>258</v>
       </c>
@@ -20195,7 +20196,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:18" hidden="1">
       <c r="A104" s="2" t="s">
         <v>260</v>
       </c>
@@ -20251,7 +20252,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:18" hidden="1">
       <c r="A105" s="2" t="s">
         <v>262</v>
       </c>
@@ -20363,7 +20364,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:18" hidden="1">
       <c r="A107" s="2" t="s">
         <v>266</v>
       </c>
@@ -20419,7 +20420,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:18" hidden="1">
       <c r="A108" s="2" t="s">
         <v>266</v>
       </c>
@@ -20475,7 +20476,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:18" hidden="1">
       <c r="A109" s="2" t="s">
         <v>268</v>
       </c>
@@ -20531,7 +20532,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="110" spans="1:18">
+    <row r="110" spans="1:18" hidden="1">
       <c r="A110" s="2" t="s">
         <v>270</v>
       </c>
@@ -20587,7 +20588,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="111" spans="1:18">
+    <row r="111" spans="1:18" hidden="1">
       <c r="A111" s="2" t="s">
         <v>272</v>
       </c>
@@ -20643,7 +20644,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="112" spans="1:18">
+    <row r="112" spans="1:18" hidden="1">
       <c r="A112" s="2" t="s">
         <v>272</v>
       </c>
@@ -20699,7 +20700,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="113" spans="1:18">
+    <row r="113" spans="1:18" hidden="1">
       <c r="A113" s="2" t="s">
         <v>274</v>
       </c>
@@ -20755,7 +20756,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="1:18">
+    <row r="114" spans="1:18" hidden="1">
       <c r="A114" s="2" t="s">
         <v>276</v>
       </c>
@@ -20811,7 +20812,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="115" spans="1:18">
+    <row r="115" spans="1:18" hidden="1">
       <c r="A115" s="2" t="s">
         <v>278</v>
       </c>
@@ -20979,7 +20980,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="118" spans="1:18">
+    <row r="118" spans="1:18" hidden="1">
       <c r="A118" s="2" t="s">
         <v>284</v>
       </c>
@@ -21035,7 +21036,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:18">
+    <row r="119" spans="1:18" hidden="1">
       <c r="A119" s="2" t="s">
         <v>286</v>
       </c>
@@ -21091,7 +21092,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="120" spans="1:18">
+    <row r="120" spans="1:18" hidden="1">
       <c r="A120" s="2" t="s">
         <v>288</v>
       </c>
@@ -21147,7 +21148,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="121" spans="1:18">
+    <row r="121" spans="1:18" hidden="1">
       <c r="A121" s="2" t="s">
         <v>288</v>
       </c>
@@ -21203,7 +21204,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="122" spans="1:18">
+    <row r="122" spans="1:18" hidden="1">
       <c r="A122" s="2" t="s">
         <v>290</v>
       </c>
@@ -21315,7 +21316,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="124" spans="1:18">
+    <row r="124" spans="1:18" hidden="1">
       <c r="A124" s="2" t="s">
         <v>294</v>
       </c>
@@ -21427,7 +21428,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="126" spans="1:18">
+    <row r="126" spans="1:18" hidden="1">
       <c r="A126" s="2" t="s">
         <v>298</v>
       </c>
@@ -21483,7 +21484,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="127" spans="1:18">
+    <row r="127" spans="1:18" hidden="1">
       <c r="A127" s="2" t="s">
         <v>300</v>
       </c>
@@ -21539,7 +21540,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="128" spans="1:18">
+    <row r="128" spans="1:18" hidden="1">
       <c r="A128" s="2" t="s">
         <v>300</v>
       </c>
@@ -21595,7 +21596,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="129" spans="1:18">
+    <row r="129" spans="1:18" hidden="1">
       <c r="A129" s="2" t="s">
         <v>302</v>
       </c>
@@ -21651,7 +21652,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="130" spans="1:18">
+    <row r="130" spans="1:18" hidden="1">
       <c r="A130" s="2" t="s">
         <v>304</v>
       </c>
@@ -21707,7 +21708,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="131" spans="1:18">
+    <row r="131" spans="1:18" hidden="1">
       <c r="A131" s="2" t="s">
         <v>306</v>
       </c>
@@ -21763,7 +21764,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="132" spans="1:18">
+    <row r="132" spans="1:18" hidden="1">
       <c r="A132" s="2" t="s">
         <v>308</v>
       </c>
@@ -21819,7 +21820,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="133" spans="1:18">
+    <row r="133" spans="1:18" hidden="1">
       <c r="A133" s="2" t="s">
         <v>310</v>
       </c>
@@ -21875,7 +21876,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="134" spans="1:18">
+    <row r="134" spans="1:18" hidden="1">
       <c r="A134" s="2" t="s">
         <v>312</v>
       </c>
@@ -21931,7 +21932,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="135" spans="1:18">
+    <row r="135" spans="1:18" hidden="1">
       <c r="A135" s="2" t="s">
         <v>314</v>
       </c>
@@ -21987,7 +21988,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="136" spans="1:18">
+    <row r="136" spans="1:18" hidden="1">
       <c r="A136" s="2" t="s">
         <v>316</v>
       </c>
@@ -22043,7 +22044,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="137" spans="1:18">
+    <row r="137" spans="1:18" hidden="1">
       <c r="A137" s="2" t="s">
         <v>318</v>
       </c>
@@ -22099,7 +22100,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="138" spans="1:18">
+    <row r="138" spans="1:18" hidden="1">
       <c r="A138" s="2" t="s">
         <v>320</v>
       </c>
@@ -22155,7 +22156,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="139" spans="1:18">
+    <row r="139" spans="1:18" hidden="1">
       <c r="A139" s="2" t="s">
         <v>322</v>
       </c>
@@ -22323,7 +22324,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:18" hidden="1">
       <c r="A142" s="2" t="s">
         <v>328</v>
       </c>
@@ -22379,7 +22380,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="143" spans="1:18">
+    <row r="143" spans="1:18" hidden="1">
       <c r="A143" s="2" t="s">
         <v>330</v>
       </c>
@@ -22435,7 +22436,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="144" spans="1:18">
+    <row r="144" spans="1:18" hidden="1">
       <c r="A144" s="2" t="s">
         <v>332</v>
       </c>
@@ -22491,7 +22492,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="145" spans="1:18">
+    <row r="145" spans="1:18" hidden="1">
       <c r="A145" s="2" t="s">
         <v>332</v>
       </c>
@@ -22547,7 +22548,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="146" spans="1:18">
+    <row r="146" spans="1:18" hidden="1">
       <c r="A146" s="2" t="s">
         <v>334</v>
       </c>
@@ -22603,7 +22604,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="147" spans="1:18">
+    <row r="147" spans="1:18" hidden="1">
       <c r="A147" s="2" t="s">
         <v>336</v>
       </c>
@@ -22659,7 +22660,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="148" spans="1:18">
+    <row r="148" spans="1:18" hidden="1">
       <c r="A148" s="2" t="s">
         <v>336</v>
       </c>
@@ -22715,7 +22716,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="149" spans="1:18">
+    <row r="149" spans="1:18" hidden="1">
       <c r="A149" s="2" t="s">
         <v>338</v>
       </c>
@@ -22771,7 +22772,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="150" spans="1:18">
+    <row r="150" spans="1:18" hidden="1">
       <c r="A150" s="2" t="s">
         <v>338</v>
       </c>
@@ -22827,7 +22828,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="151" spans="1:18">
+    <row r="151" spans="1:18" hidden="1">
       <c r="A151" s="2" t="s">
         <v>340</v>
       </c>
@@ -22883,7 +22884,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="152" spans="1:18">
+    <row r="152" spans="1:18" hidden="1">
       <c r="A152" s="2" t="s">
         <v>340</v>
       </c>
@@ -22939,7 +22940,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="153" spans="1:18">
+    <row r="153" spans="1:18" hidden="1">
       <c r="A153" s="2" t="s">
         <v>342</v>
       </c>
@@ -22995,7 +22996,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="154" spans="1:18">
+    <row r="154" spans="1:18" hidden="1">
       <c r="A154" s="2" t="s">
         <v>344</v>
       </c>
@@ -23051,7 +23052,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="155" spans="1:18">
+    <row r="155" spans="1:18" hidden="1">
       <c r="A155" s="2" t="s">
         <v>346</v>
       </c>
@@ -23163,7 +23164,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="157" spans="1:18">
+    <row r="157" spans="1:18" hidden="1">
       <c r="A157" s="2" t="s">
         <v>350</v>
       </c>
@@ -23219,7 +23220,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="158" spans="1:18">
+    <row r="158" spans="1:18" hidden="1">
       <c r="A158" s="2" t="s">
         <v>352</v>
       </c>
@@ -23275,7 +23276,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="159" spans="1:18">
+    <row r="159" spans="1:18" hidden="1">
       <c r="A159" s="2" t="s">
         <v>354</v>
       </c>
@@ -23387,7 +23388,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="161" spans="1:18">
+    <row r="161" spans="1:18" hidden="1">
       <c r="A161" s="2" t="s">
         <v>358</v>
       </c>
@@ -23499,7 +23500,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="163" spans="1:18">
+    <row r="163" spans="1:18" hidden="1">
       <c r="A163" s="2" t="s">
         <v>362</v>
       </c>
@@ -23555,7 +23556,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="164" spans="1:18">
+    <row r="164" spans="1:18" hidden="1">
       <c r="A164" s="2" t="s">
         <v>362</v>
       </c>
@@ -23611,7 +23612,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="165" spans="1:18">
+    <row r="165" spans="1:18" hidden="1">
       <c r="A165" s="2" t="s">
         <v>364</v>
       </c>
@@ -23667,7 +23668,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="166" spans="1:18">
+    <row r="166" spans="1:18" hidden="1">
       <c r="A166" s="2" t="s">
         <v>364</v>
       </c>
@@ -23723,7 +23724,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="167" spans="1:18">
+    <row r="167" spans="1:18" hidden="1">
       <c r="A167" s="2" t="s">
         <v>366</v>
       </c>
@@ -23779,7 +23780,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="168" spans="1:18">
+    <row r="168" spans="1:18" hidden="1">
       <c r="A168" s="2" t="s">
         <v>368</v>
       </c>
@@ -23835,7 +23836,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="169" spans="1:18">
+    <row r="169" spans="1:18" hidden="1">
       <c r="A169" s="2" t="s">
         <v>370</v>
       </c>
@@ -23891,7 +23892,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="170" spans="1:18">
+    <row r="170" spans="1:18" hidden="1">
       <c r="A170" s="2" t="s">
         <v>372</v>
       </c>
@@ -24171,7 +24172,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="175" spans="1:18">
+    <row r="175" spans="1:18" hidden="1">
       <c r="A175" s="2" t="s">
         <v>382</v>
       </c>
@@ -24227,7 +24228,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="176" spans="1:18">
+    <row r="176" spans="1:18" hidden="1">
       <c r="A176" s="2" t="s">
         <v>384</v>
       </c>
@@ -24283,7 +24284,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" hidden="1">
       <c r="A177" s="2" t="s">
         <v>386</v>
       </c>
@@ -24507,7 +24508,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:18" hidden="1">
       <c r="A181" s="2" t="s">
         <v>394</v>
       </c>
@@ -24563,7 +24564,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="182" spans="1:18">
+    <row r="182" spans="1:18" hidden="1">
       <c r="A182" s="2" t="s">
         <v>394</v>
       </c>
@@ -24675,7 +24676,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="184" spans="1:18">
+    <row r="184" spans="1:18" hidden="1">
       <c r="A184" s="2" t="s">
         <v>398</v>
       </c>
@@ -24731,7 +24732,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="185" spans="1:18">
+    <row r="185" spans="1:18" hidden="1">
       <c r="A185" s="2" t="s">
         <v>400</v>
       </c>
@@ -24787,7 +24788,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="186" spans="1:18">
+    <row r="186" spans="1:18" hidden="1">
       <c r="A186" s="2" t="s">
         <v>400</v>
       </c>
@@ -24899,7 +24900,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="188" spans="1:18">
+    <row r="188" spans="1:18" hidden="1">
       <c r="A188" s="2" t="s">
         <v>402</v>
       </c>
@@ -25011,7 +25012,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="190" spans="1:18">
+    <row r="190" spans="1:18" hidden="1">
       <c r="A190" s="2" t="s">
         <v>406</v>
       </c>
@@ -25067,7 +25068,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="191" spans="1:18">
+    <row r="191" spans="1:18" hidden="1">
       <c r="A191" s="2" t="s">
         <v>408</v>
       </c>
@@ -25179,7 +25180,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="193" spans="1:18">
+    <row r="193" spans="1:18" hidden="1">
       <c r="A193" s="2" t="s">
         <v>412</v>
       </c>
@@ -25291,7 +25292,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="195" spans="1:18">
+    <row r="195" spans="1:18" hidden="1">
       <c r="A195" s="2" t="s">
         <v>416</v>
       </c>
@@ -25403,7 +25404,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="197" spans="1:18">
+    <row r="197" spans="1:18" hidden="1">
       <c r="A197" s="2" t="s">
         <v>420</v>
       </c>
@@ -25459,7 +25460,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="198" spans="1:18">
+    <row r="198" spans="1:18" hidden="1">
       <c r="A198" s="2" t="s">
         <v>422</v>
       </c>
@@ -25515,7 +25516,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="199" spans="1:18">
+    <row r="199" spans="1:18" hidden="1">
       <c r="A199" s="2" t="s">
         <v>424</v>
       </c>
@@ -25571,7 +25572,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="200" spans="1:18">
+    <row r="200" spans="1:18" hidden="1">
       <c r="A200" s="2" t="s">
         <v>426</v>
       </c>
@@ -25627,7 +25628,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="201" spans="1:18">
+    <row r="201" spans="1:18" hidden="1">
       <c r="A201" s="2" t="s">
         <v>428</v>
       </c>
@@ -25683,7 +25684,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="202" spans="1:18">
+    <row r="202" spans="1:18" hidden="1">
       <c r="A202" s="2" t="s">
         <v>430</v>
       </c>
@@ -25739,7 +25740,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="203" spans="1:18">
+    <row r="203" spans="1:18" hidden="1">
       <c r="A203" s="2" t="s">
         <v>430</v>
       </c>
@@ -25795,7 +25796,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="204" spans="1:18">
+    <row r="204" spans="1:18" hidden="1">
       <c r="A204" s="2" t="s">
         <v>432</v>
       </c>
@@ -25851,7 +25852,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="205" spans="1:18">
+    <row r="205" spans="1:18" hidden="1">
       <c r="A205" s="2" t="s">
         <v>432</v>
       </c>
@@ -25907,7 +25908,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="206" spans="1:18">
+    <row r="206" spans="1:18" hidden="1">
       <c r="A206" s="2" t="s">
         <v>434</v>
       </c>
@@ -25963,7 +25964,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="207" spans="1:18">
+    <row r="207" spans="1:18" hidden="1">
       <c r="A207" s="2" t="s">
         <v>434</v>
       </c>
@@ -26019,7 +26020,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="208" spans="1:18">
+    <row r="208" spans="1:18" hidden="1">
       <c r="A208" s="2" t="s">
         <v>436</v>
       </c>
@@ -26075,7 +26076,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="209" spans="1:18">
+    <row r="209" spans="1:18" hidden="1">
       <c r="A209" s="2" t="s">
         <v>438</v>
       </c>
@@ -26131,7 +26132,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="210" spans="1:18">
+    <row r="210" spans="1:18" hidden="1">
       <c r="A210" s="2" t="s">
         <v>438</v>
       </c>
@@ -26187,7 +26188,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="211" spans="1:18">
+    <row r="211" spans="1:18" hidden="1">
       <c r="A211" s="2" t="s">
         <v>440</v>
       </c>
@@ -26243,7 +26244,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="212" spans="1:18">
+    <row r="212" spans="1:18" hidden="1">
       <c r="A212" s="2" t="s">
         <v>442</v>
       </c>
@@ -26299,7 +26300,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:18">
+    <row r="213" spans="1:18" hidden="1">
       <c r="A213" s="2" t="s">
         <v>444</v>
       </c>
@@ -26355,7 +26356,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="214" spans="1:18">
+    <row r="214" spans="1:18" hidden="1">
       <c r="A214" s="2" t="s">
         <v>444</v>
       </c>
@@ -26411,7 +26412,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="215" spans="1:18">
+    <row r="215" spans="1:18" hidden="1">
       <c r="A215" s="2" t="s">
         <v>446</v>
       </c>
@@ -26467,7 +26468,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="216" spans="1:18">
+    <row r="216" spans="1:18" hidden="1">
       <c r="A216" s="2" t="s">
         <v>448</v>
       </c>
@@ -26523,7 +26524,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="217" spans="1:18">
+    <row r="217" spans="1:18" hidden="1">
       <c r="A217" s="2" t="s">
         <v>450</v>
       </c>
@@ -26579,7 +26580,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="218" spans="1:18">
+    <row r="218" spans="1:18" hidden="1">
       <c r="A218" s="2" t="s">
         <v>452</v>
       </c>
@@ -26635,7 +26636,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="219" spans="1:18">
+    <row r="219" spans="1:18" hidden="1">
       <c r="A219" s="2" t="s">
         <v>454</v>
       </c>
@@ -26691,7 +26692,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="220" spans="1:18">
+    <row r="220" spans="1:18" hidden="1">
       <c r="A220" s="2" t="s">
         <v>454</v>
       </c>
@@ -26747,7 +26748,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="221" spans="1:18">
+    <row r="221" spans="1:18" hidden="1">
       <c r="A221" s="2" t="s">
         <v>456</v>
       </c>
@@ -26803,7 +26804,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="222" spans="1:18">
+    <row r="222" spans="1:18" hidden="1">
       <c r="A222" s="2" t="s">
         <v>456</v>
       </c>
@@ -26859,7 +26860,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="223" spans="1:18">
+    <row r="223" spans="1:18" hidden="1">
       <c r="A223" s="2" t="s">
         <v>458</v>
       </c>
@@ -26915,7 +26916,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="224" spans="1:18">
+    <row r="224" spans="1:18" hidden="1">
       <c r="A224" s="2" t="s">
         <v>460</v>
       </c>
@@ -26971,7 +26972,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="225" spans="1:18">
+    <row r="225" spans="1:18" hidden="1">
       <c r="A225" s="2" t="s">
         <v>462</v>
       </c>
@@ -27027,7 +27028,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="226" spans="1:18">
+    <row r="226" spans="1:18" hidden="1">
       <c r="A226" s="2" t="s">
         <v>464</v>
       </c>
@@ -27083,7 +27084,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="227" spans="1:18">
+    <row r="227" spans="1:18" hidden="1">
       <c r="A227" s="2" t="s">
         <v>466</v>
       </c>
@@ -27139,7 +27140,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="228" spans="1:18">
+    <row r="228" spans="1:18" hidden="1">
       <c r="A228" s="2" t="s">
         <v>466</v>
       </c>
@@ -27251,7 +27252,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="230" spans="1:18">
+    <row r="230" spans="1:18" hidden="1">
       <c r="A230" s="2" t="s">
         <v>470</v>
       </c>
@@ -27307,7 +27308,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="231" spans="1:18">
+    <row r="231" spans="1:18" hidden="1">
       <c r="A231" s="2" t="s">
         <v>472</v>
       </c>
@@ -27363,7 +27364,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="232" spans="1:18">
+    <row r="232" spans="1:18" hidden="1">
       <c r="A232" s="2" t="s">
         <v>474</v>
       </c>
@@ -27419,7 +27420,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="233" spans="1:18">
+    <row r="233" spans="1:18" hidden="1">
       <c r="A233" s="2" t="s">
         <v>474</v>
       </c>
@@ -27531,7 +27532,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="235" spans="1:18">
+    <row r="235" spans="1:18" hidden="1">
       <c r="A235" s="2" t="s">
         <v>478</v>
       </c>
@@ -27587,7 +27588,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="236" spans="1:18">
+    <row r="236" spans="1:18" hidden="1">
       <c r="A236" s="2" t="s">
         <v>480</v>
       </c>
@@ -27643,7 +27644,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="237" spans="1:18">
+    <row r="237" spans="1:18" hidden="1">
       <c r="A237" s="2" t="s">
         <v>482</v>
       </c>
@@ -27699,7 +27700,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="238" spans="1:18">
+    <row r="238" spans="1:18" hidden="1">
       <c r="A238" s="2" t="s">
         <v>484</v>
       </c>
@@ -27755,7 +27756,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="239" spans="1:18">
+    <row r="239" spans="1:18" hidden="1">
       <c r="A239" s="2" t="s">
         <v>486</v>
       </c>
@@ -27811,7 +27812,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="240" spans="1:18">
+    <row r="240" spans="1:18" hidden="1">
       <c r="A240" s="2" t="s">
         <v>488</v>
       </c>
@@ -27867,7 +27868,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="241" spans="1:18">
+    <row r="241" spans="1:18" hidden="1">
       <c r="A241" s="2" t="s">
         <v>490</v>
       </c>
@@ -27923,7 +27924,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="242" spans="1:18">
+    <row r="242" spans="1:18" hidden="1">
       <c r="A242" s="2" t="s">
         <v>492</v>
       </c>
@@ -27979,7 +27980,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="243" spans="1:18">
+    <row r="243" spans="1:18" hidden="1">
       <c r="A243" s="2" t="s">
         <v>494</v>
       </c>
@@ -28035,7 +28036,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="244" spans="1:18">
+    <row r="244" spans="1:18" hidden="1">
       <c r="A244" s="2" t="s">
         <v>496</v>
       </c>
@@ -28091,7 +28092,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="245" spans="1:18">
+    <row r="245" spans="1:18" hidden="1">
       <c r="A245" s="2" t="s">
         <v>498</v>
       </c>
@@ -28147,7 +28148,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="246" spans="1:18">
+    <row r="246" spans="1:18" hidden="1">
       <c r="A246" s="2" t="s">
         <v>500</v>
       </c>
@@ -28203,7 +28204,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="247" spans="1:18">
+    <row r="247" spans="1:18" hidden="1">
       <c r="A247" s="2" t="s">
         <v>502</v>
       </c>
@@ -28259,7 +28260,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="248" spans="1:18">
+    <row r="248" spans="1:18" hidden="1">
       <c r="A248" s="2" t="s">
         <v>504</v>
       </c>
@@ -28315,7 +28316,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="249" spans="1:18">
+    <row r="249" spans="1:18" hidden="1">
       <c r="A249" s="2" t="s">
         <v>506</v>
       </c>
@@ -28371,7 +28372,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="250" spans="1:18">
+    <row r="250" spans="1:18" hidden="1">
       <c r="A250" s="2" t="s">
         <v>508</v>
       </c>
@@ -28427,7 +28428,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="251" spans="1:18">
+    <row r="251" spans="1:18" hidden="1">
       <c r="A251" s="2" t="s">
         <v>510</v>
       </c>
@@ -28483,7 +28484,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="252" spans="1:18">
+    <row r="252" spans="1:18" hidden="1">
       <c r="A252" s="2" t="s">
         <v>512</v>
       </c>
@@ -28595,7 +28596,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="254" spans="1:18">
+    <row r="254" spans="1:18" hidden="1">
       <c r="A254" s="2" t="s">
         <v>516</v>
       </c>
@@ -28651,7 +28652,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="255" spans="1:18">
+    <row r="255" spans="1:18" hidden="1">
       <c r="A255" s="2" t="s">
         <v>518</v>
       </c>
@@ -28707,7 +28708,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="256" spans="1:18">
+    <row r="256" spans="1:18" hidden="1">
       <c r="A256" s="2" t="s">
         <v>520</v>
       </c>
@@ -28763,7 +28764,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:18" hidden="1">
       <c r="A257" s="2" t="s">
         <v>522</v>
       </c>
@@ -28819,7 +28820,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:18" hidden="1">
       <c r="A258" s="2" t="s">
         <v>524</v>
       </c>
@@ -28875,7 +28876,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:18" hidden="1">
       <c r="A259" s="2" t="s">
         <v>526</v>
       </c>
@@ -28931,7 +28932,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:18" hidden="1">
       <c r="A260" s="2" t="s">
         <v>528</v>
       </c>
@@ -28987,7 +28988,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:18" hidden="1">
       <c r="A261" s="2" t="s">
         <v>530</v>
       </c>
@@ -29099,7 +29100,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:18" hidden="1">
       <c r="A263" s="2" t="s">
         <v>534</v>
       </c>
@@ -29155,7 +29156,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="264" spans="1:18">
+    <row r="264" spans="1:18" hidden="1">
       <c r="A264" s="2" t="s">
         <v>536</v>
       </c>
@@ -29211,7 +29212,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="265" spans="1:18">
+    <row r="265" spans="1:18" hidden="1">
       <c r="A265" s="2" t="s">
         <v>538</v>
       </c>
@@ -29267,7 +29268,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="266" spans="1:18">
+    <row r="266" spans="1:18" hidden="1">
       <c r="A266" s="2" t="s">
         <v>538</v>
       </c>
@@ -29323,7 +29324,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="267" spans="1:18">
+    <row r="267" spans="1:18" hidden="1">
       <c r="A267" s="2" t="s">
         <v>538</v>
       </c>
@@ -29379,7 +29380,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="268" spans="1:18">
+    <row r="268" spans="1:18" hidden="1">
       <c r="A268" s="2" t="s">
         <v>540</v>
       </c>
@@ -29435,7 +29436,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="269" spans="1:18">
+    <row r="269" spans="1:18" hidden="1">
       <c r="A269" s="2" t="s">
         <v>540</v>
       </c>
@@ -29491,7 +29492,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="270" spans="1:18">
+    <row r="270" spans="1:18" hidden="1">
       <c r="A270" s="2" t="s">
         <v>542</v>
       </c>
@@ -29547,7 +29548,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="271" spans="1:18">
+    <row r="271" spans="1:18" hidden="1">
       <c r="A271" s="2" t="s">
         <v>544</v>
       </c>
@@ -29603,7 +29604,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="272" spans="1:18">
+    <row r="272" spans="1:18" hidden="1">
       <c r="A272" s="2" t="s">
         <v>544</v>
       </c>
@@ -29659,7 +29660,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="273" spans="1:18">
+    <row r="273" spans="1:18" hidden="1">
       <c r="A273" s="2" t="s">
         <v>546</v>
       </c>
@@ -29715,7 +29716,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="274" spans="1:18">
+    <row r="274" spans="1:18" hidden="1">
       <c r="A274" s="2" t="s">
         <v>548</v>
       </c>
@@ -29771,7 +29772,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="275" spans="1:18">
+    <row r="275" spans="1:18" hidden="1">
       <c r="A275" s="2" t="s">
         <v>550</v>
       </c>
@@ -29827,7 +29828,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="276" spans="1:18">
+    <row r="276" spans="1:18" hidden="1">
       <c r="A276" s="2" t="s">
         <v>552</v>
       </c>
@@ -29883,7 +29884,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="277" spans="1:18">
+    <row r="277" spans="1:18" hidden="1">
       <c r="A277" s="2" t="s">
         <v>554</v>
       </c>
@@ -29995,7 +29996,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="279" spans="1:18">
+    <row r="279" spans="1:18" hidden="1">
       <c r="A279" s="2" t="s">
         <v>558</v>
       </c>
@@ -30051,7 +30052,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="280" spans="1:18">
+    <row r="280" spans="1:18" hidden="1">
       <c r="A280" s="2" t="s">
         <v>560</v>
       </c>
@@ -30163,7 +30164,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="282" spans="1:18">
+    <row r="282" spans="1:18" hidden="1">
       <c r="A282" s="2" t="s">
         <v>564</v>
       </c>
@@ -30219,7 +30220,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="283" spans="1:18">
+    <row r="283" spans="1:18" hidden="1">
       <c r="A283" s="2" t="s">
         <v>566</v>
       </c>
@@ -30275,7 +30276,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="284" spans="1:18">
+    <row r="284" spans="1:18" hidden="1">
       <c r="A284" s="2" t="s">
         <v>568</v>
       </c>
@@ -30331,7 +30332,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="285" spans="1:18">
+    <row r="285" spans="1:18" hidden="1">
       <c r="A285" s="2" t="s">
         <v>570</v>
       </c>
@@ -30387,7 +30388,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="286" spans="1:18">
+    <row r="286" spans="1:18" hidden="1">
       <c r="A286" s="2" t="s">
         <v>572</v>
       </c>
@@ -30443,7 +30444,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="287" spans="1:18">
+    <row r="287" spans="1:18" hidden="1">
       <c r="A287" s="2" t="s">
         <v>574</v>
       </c>
@@ -30499,7 +30500,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="288" spans="1:18">
+    <row r="288" spans="1:18" hidden="1">
       <c r="A288" s="2" t="s">
         <v>576</v>
       </c>
@@ -30555,7 +30556,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="289" spans="1:18">
+    <row r="289" spans="1:18" hidden="1">
       <c r="A289" s="2" t="s">
         <v>576</v>
       </c>
@@ -30611,7 +30612,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="290" spans="1:18">
+    <row r="290" spans="1:18" hidden="1">
       <c r="A290" s="2" t="s">
         <v>578</v>
       </c>
@@ -30779,7 +30780,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="293" spans="1:18">
+    <row r="293" spans="1:18" hidden="1">
       <c r="A293" s="2" t="s">
         <v>584</v>
       </c>
@@ -30835,7 +30836,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:18">
+    <row r="294" spans="1:18" hidden="1">
       <c r="A294" s="2" t="s">
         <v>586</v>
       </c>
@@ -30891,7 +30892,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="295" spans="1:18">
+    <row r="295" spans="1:18" hidden="1">
       <c r="A295" s="2" t="s">
         <v>588</v>
       </c>
@@ -31003,7 +31004,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="297" spans="1:18">
+    <row r="297" spans="1:18" hidden="1">
       <c r="A297" s="2" t="s">
         <v>590</v>
       </c>
@@ -31059,7 +31060,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="298" spans="1:18">
+    <row r="298" spans="1:18" hidden="1">
       <c r="A298" s="2" t="s">
         <v>592</v>
       </c>
@@ -31115,7 +31116,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="299" spans="1:18">
+    <row r="299" spans="1:18" hidden="1">
       <c r="A299" s="2" t="s">
         <v>594</v>
       </c>
@@ -31171,7 +31172,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="300" spans="1:18">
+    <row r="300" spans="1:18" hidden="1">
       <c r="A300" s="2" t="s">
         <v>596</v>
       </c>
@@ -31227,7 +31228,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="301" spans="1:18">
+    <row r="301" spans="1:18" hidden="1">
       <c r="A301" s="2" t="s">
         <v>598</v>
       </c>
@@ -31283,7 +31284,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="302" spans="1:18">
+    <row r="302" spans="1:18" hidden="1">
       <c r="A302" s="2" t="s">
         <v>600</v>
       </c>
@@ -31339,7 +31340,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="303" spans="1:18">
+    <row r="303" spans="1:18" hidden="1">
       <c r="A303" s="2" t="s">
         <v>602</v>
       </c>
@@ -31395,7 +31396,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="304" spans="1:18">
+    <row r="304" spans="1:18" hidden="1">
       <c r="A304" s="2" t="s">
         <v>604</v>
       </c>
@@ -31451,7 +31452,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="305" spans="1:18">
+    <row r="305" spans="1:18" hidden="1">
       <c r="A305" s="2" t="s">
         <v>606</v>
       </c>
@@ -31563,7 +31564,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="307" spans="1:18">
+    <row r="307" spans="1:18" hidden="1">
       <c r="A307" s="2" t="s">
         <v>610</v>
       </c>
@@ -31619,7 +31620,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="308" spans="1:18">
+    <row r="308" spans="1:18" hidden="1">
       <c r="A308" s="2" t="s">
         <v>612</v>
       </c>
@@ -31675,7 +31676,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="309" spans="1:18">
+    <row r="309" spans="1:18" hidden="1">
       <c r="A309" s="2" t="s">
         <v>614</v>
       </c>
@@ -31731,7 +31732,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="310" spans="1:18">
+    <row r="310" spans="1:18" hidden="1">
       <c r="A310" s="2" t="s">
         <v>616</v>
       </c>
@@ -31787,7 +31788,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="311" spans="1:18">
+    <row r="311" spans="1:18" hidden="1">
       <c r="A311" s="2" t="s">
         <v>618</v>
       </c>
@@ -31843,7 +31844,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="312" spans="1:18">
+    <row r="312" spans="1:18" hidden="1">
       <c r="A312" s="2" t="s">
         <v>620</v>
       </c>
@@ -31899,7 +31900,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="313" spans="1:18">
+    <row r="313" spans="1:18" hidden="1">
       <c r="A313" s="2" t="s">
         <v>622</v>
       </c>
@@ -31955,7 +31956,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="314" spans="1:18">
+    <row r="314" spans="1:18" hidden="1">
       <c r="A314" s="2" t="s">
         <v>622</v>
       </c>
@@ -32011,7 +32012,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="315" spans="1:18">
+    <row r="315" spans="1:18" hidden="1">
       <c r="A315" s="2" t="s">
         <v>624</v>
       </c>
@@ -32067,7 +32068,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="316" spans="1:18">
+    <row r="316" spans="1:18" hidden="1">
       <c r="A316" s="2" t="s">
         <v>626</v>
       </c>
@@ -32123,7 +32124,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="317" spans="1:18">
+    <row r="317" spans="1:18" hidden="1">
       <c r="A317" s="2" t="s">
         <v>626</v>
       </c>
@@ -32179,7 +32180,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="318" spans="1:18">
+    <row r="318" spans="1:18" hidden="1">
       <c r="A318" s="2" t="s">
         <v>628</v>
       </c>
@@ -32235,7 +32236,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="319" spans="1:18">
+    <row r="319" spans="1:18" hidden="1">
       <c r="A319" s="2" t="s">
         <v>630</v>
       </c>
@@ -32459,7 +32460,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="323" spans="1:18">
+    <row r="323" spans="1:18" hidden="1">
       <c r="A323" s="2" t="s">
         <v>638</v>
       </c>
@@ -32515,7 +32516,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="324" spans="1:18">
+    <row r="324" spans="1:18" hidden="1">
       <c r="A324" s="2" t="s">
         <v>638</v>
       </c>
@@ -32571,7 +32572,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="325" spans="1:18">
+    <row r="325" spans="1:18" hidden="1">
       <c r="A325" s="2" t="s">
         <v>640</v>
       </c>
@@ -32627,7 +32628,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="326" spans="1:18">
+    <row r="326" spans="1:18" hidden="1">
       <c r="A326" s="2" t="s">
         <v>642</v>
       </c>
@@ -32683,7 +32684,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="327" spans="1:18">
+    <row r="327" spans="1:18" hidden="1">
       <c r="A327" s="2" t="s">
         <v>642</v>
       </c>
@@ -32739,7 +32740,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="328" spans="1:18">
+    <row r="328" spans="1:18" hidden="1">
       <c r="A328" s="2" t="s">
         <v>644</v>
       </c>
@@ -32795,7 +32796,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="329" spans="1:18">
+    <row r="329" spans="1:18" hidden="1">
       <c r="A329" s="2" t="s">
         <v>646</v>
       </c>
@@ -32851,7 +32852,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="330" spans="1:18">
+    <row r="330" spans="1:18" hidden="1">
       <c r="A330" s="2" t="s">
         <v>648</v>
       </c>
@@ -32907,7 +32908,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="331" spans="1:18">
+    <row r="331" spans="1:18" hidden="1">
       <c r="A331" s="2" t="s">
         <v>650</v>
       </c>
@@ -32963,7 +32964,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="332" spans="1:18">
+    <row r="332" spans="1:18" hidden="1">
       <c r="A332" s="2" t="s">
         <v>650</v>
       </c>
@@ -33019,7 +33020,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="333" spans="1:18">
+    <row r="333" spans="1:18" hidden="1">
       <c r="A333" s="2" t="s">
         <v>652</v>
       </c>
@@ -33075,7 +33076,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="334" spans="1:18">
+    <row r="334" spans="1:18" hidden="1">
       <c r="A334" s="2" t="s">
         <v>654</v>
       </c>
@@ -33131,7 +33132,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="335" spans="1:18">
+    <row r="335" spans="1:18" hidden="1">
       <c r="A335" s="2" t="s">
         <v>656</v>
       </c>
@@ -33187,7 +33188,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:18">
+    <row r="336" spans="1:18" hidden="1">
       <c r="A336" s="2" t="s">
         <v>658</v>
       </c>
@@ -33243,7 +33244,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="337" spans="1:18">
+    <row r="337" spans="1:18" hidden="1">
       <c r="A337" s="2" t="s">
         <v>660</v>
       </c>
@@ -33299,7 +33300,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="338" spans="1:18">
+    <row r="338" spans="1:18" hidden="1">
       <c r="A338" s="2" t="s">
         <v>662</v>
       </c>
@@ -33355,7 +33356,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="339" spans="1:18">
+    <row r="339" spans="1:18" hidden="1">
       <c r="A339" s="2" t="s">
         <v>662</v>
       </c>
@@ -33411,7 +33412,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="340" spans="1:18">
+    <row r="340" spans="1:18" hidden="1">
       <c r="A340" s="2" t="s">
         <v>665</v>
       </c>
@@ -33467,7 +33468,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="341" spans="1:18">
+    <row r="341" spans="1:18" hidden="1">
       <c r="A341" s="2" t="s">
         <v>667</v>
       </c>
@@ -33523,7 +33524,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="342" spans="1:18">
+    <row r="342" spans="1:18" hidden="1">
       <c r="A342" s="2" t="s">
         <v>667</v>
       </c>
@@ -33579,7 +33580,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="343" spans="1:18">
+    <row r="343" spans="1:18" hidden="1">
       <c r="A343" s="2" t="s">
         <v>669</v>
       </c>
@@ -33635,7 +33636,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="344" spans="1:18">
+    <row r="344" spans="1:18" hidden="1">
       <c r="A344" s="2" t="s">
         <v>671</v>
       </c>
@@ -33691,7 +33692,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="345" spans="1:18">
+    <row r="345" spans="1:18" hidden="1">
       <c r="A345" s="2" t="s">
         <v>673</v>
       </c>
@@ -33915,7 +33916,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="349" spans="1:18">
+    <row r="349" spans="1:18" hidden="1">
       <c r="A349" s="2" t="s">
         <v>681</v>
       </c>
@@ -33971,7 +33972,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="350" spans="1:18">
+    <row r="350" spans="1:18" hidden="1">
       <c r="A350" s="2" t="s">
         <v>683</v>
       </c>
@@ -34027,7 +34028,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="351" spans="1:18">
+    <row r="351" spans="1:18" hidden="1">
       <c r="A351" s="2" t="s">
         <v>683</v>
       </c>
@@ -34083,7 +34084,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="352" spans="1:18">
+    <row r="352" spans="1:18" hidden="1">
       <c r="A352" s="2" t="s">
         <v>685</v>
       </c>
@@ -34195,7 +34196,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="354" spans="1:18">
+    <row r="354" spans="1:18" hidden="1">
       <c r="A354" s="2" t="s">
         <v>689</v>
       </c>
@@ -34251,7 +34252,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="355" spans="1:18">
+    <row r="355" spans="1:18" hidden="1">
       <c r="A355" s="2" t="s">
         <v>691</v>
       </c>
@@ -34307,7 +34308,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="356" spans="1:18">
+    <row r="356" spans="1:18" hidden="1">
       <c r="A356" s="2" t="s">
         <v>693</v>
       </c>
@@ -34363,7 +34364,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="357" spans="1:18">
+    <row r="357" spans="1:18" hidden="1">
       <c r="A357" s="2" t="s">
         <v>695</v>
       </c>
@@ -34419,7 +34420,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="358" spans="1:18">
+    <row r="358" spans="1:18" hidden="1">
       <c r="A358" s="2" t="s">
         <v>697</v>
       </c>
@@ -34531,7 +34532,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="360" spans="1:18">
+    <row r="360" spans="1:18" hidden="1">
       <c r="A360" s="2" t="s">
         <v>701</v>
       </c>
@@ -34587,7 +34588,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="361" spans="1:18">
+    <row r="361" spans="1:18" hidden="1">
       <c r="A361" s="2" t="s">
         <v>703</v>
       </c>
@@ -34643,7 +34644,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="362" spans="1:18">
+    <row r="362" spans="1:18" hidden="1">
       <c r="A362" s="2" t="s">
         <v>705</v>
       </c>
@@ -34699,7 +34700,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="363" spans="1:18">
+    <row r="363" spans="1:18" hidden="1">
       <c r="A363" s="2" t="s">
         <v>707</v>
       </c>
@@ -34755,7 +34756,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="364" spans="1:18">
+    <row r="364" spans="1:18" hidden="1">
       <c r="A364" s="2" t="s">
         <v>709</v>
       </c>
@@ -34811,7 +34812,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="365" spans="1:18">
+    <row r="365" spans="1:18" hidden="1">
       <c r="A365" s="2" t="s">
         <v>711</v>
       </c>
@@ -34867,7 +34868,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="366" spans="1:18">
+    <row r="366" spans="1:18" hidden="1">
       <c r="A366" s="2" t="s">
         <v>713</v>
       </c>
@@ -34923,7 +34924,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="367" spans="1:18">
+    <row r="367" spans="1:18" hidden="1">
       <c r="A367" s="2" t="s">
         <v>715</v>
       </c>
@@ -34979,7 +34980,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="368" spans="1:18">
+    <row r="368" spans="1:18" hidden="1">
       <c r="A368" s="2" t="s">
         <v>717</v>
       </c>
@@ -35035,7 +35036,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="369" spans="1:18">
+    <row r="369" spans="1:18" hidden="1">
       <c r="A369" s="2" t="s">
         <v>719</v>
       </c>
@@ -35091,7 +35092,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="370" spans="1:18">
+    <row r="370" spans="1:18" hidden="1">
       <c r="A370" s="2" t="s">
         <v>721</v>
       </c>
@@ -35147,7 +35148,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="371" spans="1:18">
+    <row r="371" spans="1:18" hidden="1">
       <c r="A371" s="2" t="s">
         <v>721</v>
       </c>
@@ -35203,7 +35204,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="372" spans="1:18">
+    <row r="372" spans="1:18" hidden="1">
       <c r="A372" s="2" t="s">
         <v>723</v>
       </c>
@@ -35259,7 +35260,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="373" spans="1:18">
+    <row r="373" spans="1:18" hidden="1">
       <c r="A373" s="2" t="s">
         <v>725</v>
       </c>
@@ -35315,7 +35316,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="374" spans="1:18">
+    <row r="374" spans="1:18" hidden="1">
       <c r="A374" s="2" t="s">
         <v>727</v>
       </c>
@@ -35371,7 +35372,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="375" spans="1:18">
+    <row r="375" spans="1:18" hidden="1">
       <c r="A375" s="2" t="s">
         <v>727</v>
       </c>
@@ -35427,7 +35428,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="376" spans="1:18">
+    <row r="376" spans="1:18" hidden="1">
       <c r="A376" s="2" t="s">
         <v>729</v>
       </c>
@@ -35483,7 +35484,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="377" spans="1:18">
+    <row r="377" spans="1:18" hidden="1">
       <c r="A377" s="2" t="s">
         <v>731</v>
       </c>
@@ -35539,7 +35540,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="378" spans="1:18">
+    <row r="378" spans="1:18" hidden="1">
       <c r="A378" s="2" t="s">
         <v>733</v>
       </c>
@@ -35595,7 +35596,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="379" spans="1:18">
+    <row r="379" spans="1:18" hidden="1">
       <c r="A379" s="2" t="s">
         <v>735</v>
       </c>
@@ -35651,7 +35652,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="380" spans="1:18">
+    <row r="380" spans="1:18" hidden="1">
       <c r="A380" s="2" t="s">
         <v>737</v>
       </c>
@@ -35707,7 +35708,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="381" spans="1:18">
+    <row r="381" spans="1:18" hidden="1">
       <c r="A381" s="2" t="s">
         <v>739</v>
       </c>
@@ -35763,7 +35764,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="382" spans="1:18">
+    <row r="382" spans="1:18" hidden="1">
       <c r="A382" s="2" t="s">
         <v>741</v>
       </c>
@@ -35819,7 +35820,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="383" spans="1:18">
+    <row r="383" spans="1:18" hidden="1">
       <c r="A383" s="2" t="s">
         <v>743</v>
       </c>
@@ -35875,7 +35876,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="384" spans="1:18">
+    <row r="384" spans="1:18" hidden="1">
       <c r="A384" s="2" t="s">
         <v>743</v>
       </c>
@@ -35931,7 +35932,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="385" spans="1:18">
+    <row r="385" spans="1:18" hidden="1">
       <c r="A385" s="2" t="s">
         <v>745</v>
       </c>
@@ -35987,7 +35988,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="386" spans="1:18">
+    <row r="386" spans="1:18" hidden="1">
       <c r="A386" s="2" t="s">
         <v>747</v>
       </c>
@@ -36099,7 +36100,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="388" spans="1:18">
+    <row r="388" spans="1:18" hidden="1">
       <c r="A388" s="2" t="s">
         <v>751</v>
       </c>
@@ -36155,7 +36156,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="389" spans="1:18">
+    <row r="389" spans="1:18" hidden="1">
       <c r="A389" s="2" t="s">
         <v>753</v>
       </c>
@@ -36211,7 +36212,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="390" spans="1:18">
+    <row r="390" spans="1:18" hidden="1">
       <c r="A390" s="2" t="s">
         <v>755</v>
       </c>
@@ -36267,7 +36268,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="391" spans="1:18">
+    <row r="391" spans="1:18" hidden="1">
       <c r="A391" s="2" t="s">
         <v>757</v>
       </c>
@@ -36323,7 +36324,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="392" spans="1:18">
+    <row r="392" spans="1:18" hidden="1">
       <c r="A392" s="2" t="s">
         <v>759</v>
       </c>
@@ -36435,7 +36436,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="394" spans="1:18">
+    <row r="394" spans="1:18" hidden="1">
       <c r="A394" s="2" t="s">
         <v>763</v>
       </c>
@@ -36547,7 +36548,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="396" spans="1:18">
+    <row r="396" spans="1:18" hidden="1">
       <c r="A396" s="2" t="s">
         <v>767</v>
       </c>
@@ -36603,7 +36604,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="397" spans="1:18">
+    <row r="397" spans="1:18" hidden="1">
       <c r="A397" s="2" t="s">
         <v>769</v>
       </c>
@@ -36659,7 +36660,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="398" spans="1:18">
+    <row r="398" spans="1:18" hidden="1">
       <c r="A398" s="2" t="s">
         <v>771</v>
       </c>
@@ -36715,7 +36716,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="399" spans="1:18">
+    <row r="399" spans="1:18" hidden="1">
       <c r="A399" s="2" t="s">
         <v>771</v>
       </c>
@@ -36771,7 +36772,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="400" spans="1:18">
+    <row r="400" spans="1:18" hidden="1">
       <c r="A400" s="2" t="s">
         <v>773</v>
       </c>
@@ -36827,7 +36828,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="401" spans="1:18">
+    <row r="401" spans="1:18" hidden="1">
       <c r="A401" s="2" t="s">
         <v>773</v>
       </c>
@@ -36939,7 +36940,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="403" spans="1:18">
+    <row r="403" spans="1:18" hidden="1">
       <c r="A403" s="2" t="s">
         <v>777</v>
       </c>
@@ -36995,7 +36996,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="404" spans="1:18">
+    <row r="404" spans="1:18" hidden="1">
       <c r="A404" s="2" t="s">
         <v>779</v>
       </c>
@@ -37051,7 +37052,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="405" spans="1:18">
+    <row r="405" spans="1:18" hidden="1">
       <c r="A405" s="2" t="s">
         <v>781</v>
       </c>
@@ -37107,7 +37108,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="406" spans="1:18">
+    <row r="406" spans="1:18" hidden="1">
       <c r="A406" s="2" t="s">
         <v>783</v>
       </c>
@@ -37163,7 +37164,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="407" spans="1:18">
+    <row r="407" spans="1:18" hidden="1">
       <c r="A407" s="2" t="s">
         <v>785</v>
       </c>
@@ -37219,7 +37220,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="408" spans="1:18">
+    <row r="408" spans="1:18" hidden="1">
       <c r="A408" s="2" t="s">
         <v>787</v>
       </c>
@@ -37331,7 +37332,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="410" spans="1:18">
+    <row r="410" spans="1:18" hidden="1">
       <c r="A410" s="2" t="s">
         <v>791</v>
       </c>
@@ -37387,7 +37388,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="411" spans="1:18">
+    <row r="411" spans="1:18" hidden="1">
       <c r="A411" s="2" t="s">
         <v>793</v>
       </c>
@@ -37443,7 +37444,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="412" spans="1:18">
+    <row r="412" spans="1:18" hidden="1">
       <c r="A412" s="2" t="s">
         <v>795</v>
       </c>
@@ -37555,7 +37556,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="414" spans="1:18">
+    <row r="414" spans="1:18" hidden="1">
       <c r="A414" s="2" t="s">
         <v>799</v>
       </c>
@@ -37611,7 +37612,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="415" spans="1:18">
+    <row r="415" spans="1:18" hidden="1">
       <c r="A415" s="2" t="s">
         <v>799</v>
       </c>
@@ -37667,7 +37668,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="416" spans="1:18">
+    <row r="416" spans="1:18" hidden="1">
       <c r="A416" s="2" t="s">
         <v>799</v>
       </c>
@@ -37723,7 +37724,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="417" spans="1:18">
+    <row r="417" spans="1:18" hidden="1">
       <c r="A417" s="2" t="s">
         <v>801</v>
       </c>
@@ -37779,7 +37780,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="418" spans="1:18">
+    <row r="418" spans="1:18" hidden="1">
       <c r="A418" s="2" t="s">
         <v>803</v>
       </c>
@@ -37835,7 +37836,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="419" spans="1:18">
+    <row r="419" spans="1:18" hidden="1">
       <c r="A419" s="2" t="s">
         <v>805</v>
       </c>
@@ -37891,7 +37892,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="420" spans="1:18">
+    <row r="420" spans="1:18" hidden="1">
       <c r="A420" s="2" t="s">
         <v>807</v>
       </c>
@@ -37947,7 +37948,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="421" spans="1:18">
+    <row r="421" spans="1:18" hidden="1">
       <c r="A421" s="2" t="s">
         <v>809</v>
       </c>
@@ -38003,7 +38004,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="422" spans="1:18">
+    <row r="422" spans="1:18" hidden="1">
       <c r="A422" s="2" t="s">
         <v>811</v>
       </c>
@@ -38059,7 +38060,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="423" spans="1:18">
+    <row r="423" spans="1:18" hidden="1">
       <c r="A423" s="2" t="s">
         <v>813</v>
       </c>
@@ -38115,7 +38116,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="424" spans="1:18">
+    <row r="424" spans="1:18" hidden="1">
       <c r="A424" s="2" t="s">
         <v>815</v>
       </c>
@@ -38171,7 +38172,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="425" spans="1:18">
+    <row r="425" spans="1:18" hidden="1">
       <c r="A425" s="2" t="s">
         <v>817</v>
       </c>
@@ -38227,7 +38228,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="426" spans="1:18">
+    <row r="426" spans="1:18" hidden="1">
       <c r="A426" s="2" t="s">
         <v>819</v>
       </c>
@@ -38283,7 +38284,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="427" spans="1:18">
+    <row r="427" spans="1:18" hidden="1">
       <c r="A427" s="2" t="s">
         <v>821</v>
       </c>
@@ -38339,7 +38340,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="428" spans="1:18">
+    <row r="428" spans="1:18" hidden="1">
       <c r="A428" s="2" t="s">
         <v>823</v>
       </c>
@@ -38395,7 +38396,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="429" spans="1:18">
+    <row r="429" spans="1:18" hidden="1">
       <c r="A429" s="2" t="s">
         <v>823</v>
       </c>
@@ -38451,7 +38452,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="430" spans="1:18">
+    <row r="430" spans="1:18" hidden="1">
       <c r="A430" s="2" t="s">
         <v>825</v>
       </c>
@@ -38507,7 +38508,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="431" spans="1:18">
+    <row r="431" spans="1:18" hidden="1">
       <c r="A431" s="2" t="s">
         <v>827</v>
       </c>
@@ -38563,7 +38564,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="432" spans="1:18">
+    <row r="432" spans="1:18" hidden="1">
       <c r="A432" s="2" t="s">
         <v>829</v>
       </c>
@@ -38619,7 +38620,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="433" spans="1:18">
+    <row r="433" spans="1:18" hidden="1">
       <c r="A433" s="2" t="s">
         <v>831</v>
       </c>
@@ -38675,7 +38676,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="434" spans="1:18">
+    <row r="434" spans="1:18" hidden="1">
       <c r="A434" s="2" t="s">
         <v>833</v>
       </c>
@@ -38731,7 +38732,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="435" spans="1:18">
+    <row r="435" spans="1:18" hidden="1">
       <c r="A435" s="2" t="s">
         <v>835</v>
       </c>
@@ -38787,7 +38788,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="436" spans="1:18">
+    <row r="436" spans="1:18" hidden="1">
       <c r="A436" s="2" t="s">
         <v>837</v>
       </c>
@@ -38843,7 +38844,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="437" spans="1:18">
+    <row r="437" spans="1:18" hidden="1">
       <c r="A437" s="2" t="s">
         <v>839</v>
       </c>
@@ -38899,7 +38900,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="438" spans="1:18">
+    <row r="438" spans="1:18" hidden="1">
       <c r="A438" s="2" t="s">
         <v>841</v>
       </c>
@@ -38955,7 +38956,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="439" spans="1:18">
+    <row r="439" spans="1:18" hidden="1">
       <c r="A439" s="2" t="s">
         <v>843</v>
       </c>
@@ -39011,7 +39012,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="440" spans="1:18">
+    <row r="440" spans="1:18" hidden="1">
       <c r="A440" s="2" t="s">
         <v>845</v>
       </c>
@@ -39067,7 +39068,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="441" spans="1:18">
+    <row r="441" spans="1:18" hidden="1">
       <c r="A441" s="2" t="s">
         <v>847</v>
       </c>
@@ -39123,7 +39124,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="442" spans="1:18">
+    <row r="442" spans="1:18" hidden="1">
       <c r="A442" s="2" t="s">
         <v>849</v>
       </c>
@@ -39179,7 +39180,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="443" spans="1:18">
+    <row r="443" spans="1:18" hidden="1">
       <c r="A443" s="2" t="s">
         <v>851</v>
       </c>
@@ -39235,7 +39236,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="444" spans="1:18">
+    <row r="444" spans="1:18" hidden="1">
       <c r="A444" s="2" t="s">
         <v>851</v>
       </c>
@@ -39291,7 +39292,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="445" spans="1:18">
+    <row r="445" spans="1:18" hidden="1">
       <c r="A445" s="2" t="s">
         <v>853</v>
       </c>
@@ -39347,7 +39348,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="446" spans="1:18">
+    <row r="446" spans="1:18" hidden="1">
       <c r="A446" s="2" t="s">
         <v>853</v>
       </c>
@@ -39403,7 +39404,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="447" spans="1:18">
+    <row r="447" spans="1:18" hidden="1">
       <c r="A447" s="2" t="s">
         <v>855</v>
       </c>
@@ -39459,7 +39460,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="448" spans="1:18">
+    <row r="448" spans="1:18" hidden="1">
       <c r="A448" s="2" t="s">
         <v>857</v>
       </c>
@@ -39515,7 +39516,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="449" spans="1:18">
+    <row r="449" spans="1:18" hidden="1">
       <c r="A449" s="2" t="s">
         <v>857</v>
       </c>
@@ -39571,7 +39572,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="450" spans="1:18">
+    <row r="450" spans="1:18" hidden="1">
       <c r="A450" s="2" t="s">
         <v>859</v>
       </c>
@@ -39627,7 +39628,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="451" spans="1:18">
+    <row r="451" spans="1:18" hidden="1">
       <c r="A451" s="2" t="s">
         <v>859</v>
       </c>
@@ -39683,7 +39684,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="452" spans="1:18">
+    <row r="452" spans="1:18" hidden="1">
       <c r="A452" s="2" t="s">
         <v>861</v>
       </c>
@@ -39739,7 +39740,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="453" spans="1:18">
+    <row r="453" spans="1:18" hidden="1">
       <c r="A453" s="2" t="s">
         <v>863</v>
       </c>
@@ -39907,7 +39908,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="456" spans="1:18">
+    <row r="456" spans="1:18" hidden="1">
       <c r="A456" s="2" t="s">
         <v>869</v>
       </c>
@@ -40019,7 +40020,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="458" spans="1:18">
+    <row r="458" spans="1:18" hidden="1">
       <c r="A458" s="2" t="s">
         <v>873</v>
       </c>
@@ -40075,7 +40076,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="459" spans="1:18">
+    <row r="459" spans="1:18" hidden="1">
       <c r="A459" s="2" t="s">
         <v>873</v>
       </c>
@@ -40131,7 +40132,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="460" spans="1:18">
+    <row r="460" spans="1:18" hidden="1">
       <c r="A460" s="2" t="s">
         <v>875</v>
       </c>
@@ -40187,7 +40188,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="461" spans="1:18">
+    <row r="461" spans="1:18" hidden="1">
       <c r="A461" s="2" t="s">
         <v>877</v>
       </c>
@@ -40299,7 +40300,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="463" spans="1:18">
+    <row r="463" spans="1:18" hidden="1">
       <c r="A463" s="2" t="s">
         <v>881</v>
       </c>
@@ -40355,7 +40356,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="464" spans="1:18">
+    <row r="464" spans="1:18" hidden="1">
       <c r="A464" s="2" t="s">
         <v>883</v>
       </c>
@@ -40411,7 +40412,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="465" spans="1:18">
+    <row r="465" spans="1:18" hidden="1">
       <c r="A465" s="2" t="s">
         <v>885</v>
       </c>
@@ -40467,7 +40468,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="466" spans="1:18">
+    <row r="466" spans="1:18" hidden="1">
       <c r="A466" s="2" t="s">
         <v>885</v>
       </c>
@@ -40523,7 +40524,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="467" spans="1:18">
+    <row r="467" spans="1:18" hidden="1">
       <c r="A467" s="2" t="s">
         <v>887</v>
       </c>
@@ -40579,7 +40580,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="468" spans="1:18">
+    <row r="468" spans="1:18" hidden="1">
       <c r="A468" s="2" t="s">
         <v>887</v>
       </c>
@@ -40635,7 +40636,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="469" spans="1:18">
+    <row r="469" spans="1:18" hidden="1">
       <c r="A469" s="2" t="s">
         <v>889</v>
       </c>
@@ -40691,7 +40692,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="470" spans="1:18">
+    <row r="470" spans="1:18" hidden="1">
       <c r="A470" s="2" t="s">
         <v>891</v>
       </c>
@@ -40747,7 +40748,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="471" spans="1:18">
+    <row r="471" spans="1:18" hidden="1">
       <c r="A471" s="2" t="s">
         <v>893</v>
       </c>
@@ -40803,7 +40804,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="472" spans="1:18">
+    <row r="472" spans="1:18" hidden="1">
       <c r="A472" s="2" t="s">
         <v>895</v>
       </c>
@@ -40859,7 +40860,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="473" spans="1:18">
+    <row r="473" spans="1:18" hidden="1">
       <c r="A473" s="2" t="s">
         <v>897</v>
       </c>
@@ -40915,7 +40916,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="474" spans="1:18">
+    <row r="474" spans="1:18" hidden="1">
       <c r="A474" s="2" t="s">
         <v>899</v>
       </c>
@@ -40971,7 +40972,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="475" spans="1:18">
+    <row r="475" spans="1:18" hidden="1">
       <c r="A475" s="2" t="s">
         <v>899</v>
       </c>
@@ -41083,7 +41084,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="477" spans="1:18">
+    <row r="477" spans="1:18" hidden="1">
       <c r="A477" s="2" t="s">
         <v>903</v>
       </c>
@@ -41139,7 +41140,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="478" spans="1:18">
+    <row r="478" spans="1:18" hidden="1">
       <c r="A478" s="2" t="s">
         <v>905</v>
       </c>
@@ -41195,7 +41196,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="479" spans="1:18">
+    <row r="479" spans="1:18" hidden="1">
       <c r="A479" s="2" t="s">
         <v>907</v>
       </c>
@@ -41251,7 +41252,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="480" spans="1:18">
+    <row r="480" spans="1:18" hidden="1">
       <c r="A480" s="2" t="s">
         <v>907</v>
       </c>
@@ -41307,7 +41308,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="481" spans="1:18">
+    <row r="481" spans="1:18" hidden="1">
       <c r="A481" s="2" t="s">
         <v>909</v>
       </c>
@@ -41363,7 +41364,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="482" spans="1:18">
+    <row r="482" spans="1:18" hidden="1">
       <c r="A482" s="2" t="s">
         <v>911</v>
       </c>
@@ -41419,7 +41420,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="483" spans="1:18">
+    <row r="483" spans="1:18" hidden="1">
       <c r="A483" s="2" t="s">
         <v>913</v>
       </c>
@@ -41475,7 +41476,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="484" spans="1:18">
+    <row r="484" spans="1:18" hidden="1">
       <c r="A484" s="2" t="s">
         <v>915</v>
       </c>
@@ -41531,7 +41532,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="485" spans="1:18">
+    <row r="485" spans="1:18" hidden="1">
       <c r="A485" s="2" t="s">
         <v>917</v>
       </c>
@@ -41587,7 +41588,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="486" spans="1:18">
+    <row r="486" spans="1:18" hidden="1">
       <c r="A486" s="2" t="s">
         <v>919</v>
       </c>
@@ -41643,7 +41644,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="487" spans="1:18">
+    <row r="487" spans="1:18" hidden="1">
       <c r="A487" s="2" t="s">
         <v>921</v>
       </c>
@@ -41699,7 +41700,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="488" spans="1:18">
+    <row r="488" spans="1:18" hidden="1">
       <c r="A488" s="2" t="s">
         <v>923</v>
       </c>
@@ -41755,7 +41756,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="489" spans="1:18">
+    <row r="489" spans="1:18" hidden="1">
       <c r="A489" s="2" t="s">
         <v>925</v>
       </c>
@@ -41811,7 +41812,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="490" spans="1:18">
+    <row r="490" spans="1:18" hidden="1">
       <c r="A490" s="2" t="s">
         <v>927</v>
       </c>
@@ -41867,7 +41868,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="491" spans="1:18">
+    <row r="491" spans="1:18" hidden="1">
       <c r="A491" s="2" t="s">
         <v>929</v>
       </c>
@@ -41923,7 +41924,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="492" spans="1:18">
+    <row r="492" spans="1:18" hidden="1">
       <c r="A492" s="2" t="s">
         <v>931</v>
       </c>
@@ -41979,7 +41980,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="493" spans="1:18">
+    <row r="493" spans="1:18" hidden="1">
       <c r="A493" s="2" t="s">
         <v>931</v>
       </c>
@@ -42035,7 +42036,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="494" spans="1:18">
+    <row r="494" spans="1:18" hidden="1">
       <c r="A494" s="2" t="s">
         <v>933</v>
       </c>
@@ -42147,7 +42148,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="496" spans="1:18">
+    <row r="496" spans="1:18" hidden="1">
       <c r="A496" s="2" t="s">
         <v>937</v>
       </c>
@@ -42203,7 +42204,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="497" spans="1:18">
+    <row r="497" spans="1:18" hidden="1">
       <c r="A497" s="2" t="s">
         <v>939</v>
       </c>
@@ -42259,7 +42260,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="498" spans="1:18">
+    <row r="498" spans="1:18" hidden="1">
       <c r="A498" s="2" t="s">
         <v>941</v>
       </c>
@@ -42315,7 +42316,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="499" spans="1:18">
+    <row r="499" spans="1:18" hidden="1">
       <c r="A499" s="2" t="s">
         <v>943</v>
       </c>
@@ -42371,7 +42372,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="500" spans="1:18">
+    <row r="500" spans="1:18" hidden="1">
       <c r="A500" s="2" t="s">
         <v>945</v>
       </c>
@@ -42539,7 +42540,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="503" spans="1:18">
+    <row r="503" spans="1:18" hidden="1">
       <c r="A503" s="2" t="s">
         <v>951</v>
       </c>
@@ -42595,7 +42596,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="504" spans="1:18">
+    <row r="504" spans="1:18" hidden="1">
       <c r="A504" s="2" t="s">
         <v>953</v>
       </c>
@@ -42651,7 +42652,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="505" spans="1:18">
+    <row r="505" spans="1:18" hidden="1">
       <c r="A505" s="2" t="s">
         <v>953</v>
       </c>
@@ -42707,7 +42708,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="506" spans="1:18">
+    <row r="506" spans="1:18" hidden="1">
       <c r="A506" s="2" t="s">
         <v>955</v>
       </c>
@@ -42763,7 +42764,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="507" spans="1:18">
+    <row r="507" spans="1:18" hidden="1">
       <c r="A507" s="2" t="s">
         <v>957</v>
       </c>
@@ -42819,7 +42820,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="508" spans="1:18">
+    <row r="508" spans="1:18" hidden="1">
       <c r="A508" s="2" t="s">
         <v>957</v>
       </c>
@@ -42875,7 +42876,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="509" spans="1:18">
+    <row r="509" spans="1:18" hidden="1">
       <c r="A509" s="2" t="s">
         <v>959</v>
       </c>
@@ -42931,7 +42932,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="510" spans="1:18">
+    <row r="510" spans="1:18" hidden="1">
       <c r="A510" s="2" t="s">
         <v>961</v>
       </c>
@@ -42987,7 +42988,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="511" spans="1:18">
+    <row r="511" spans="1:18" hidden="1">
       <c r="A511" s="2" t="s">
         <v>963</v>
       </c>
@@ -43043,7 +43044,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="512" spans="1:18">
+    <row r="512" spans="1:18" hidden="1">
       <c r="A512" s="2" t="s">
         <v>965</v>
       </c>
@@ -43099,7 +43100,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="513" spans="1:18">
+    <row r="513" spans="1:18" hidden="1">
       <c r="A513" s="2" t="s">
         <v>967</v>
       </c>
@@ -43155,7 +43156,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="514" spans="1:18">
+    <row r="514" spans="1:18" hidden="1">
       <c r="A514" s="2" t="s">
         <v>969</v>
       </c>
@@ -43211,7 +43212,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="515" spans="1:18">
+    <row r="515" spans="1:18" hidden="1">
       <c r="A515" s="2" t="s">
         <v>971</v>
       </c>
@@ -43267,7 +43268,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="516" spans="1:18">
+    <row r="516" spans="1:18" hidden="1">
       <c r="A516" s="2" t="s">
         <v>973</v>
       </c>
@@ -43323,7 +43324,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="517" spans="1:18">
+    <row r="517" spans="1:18" hidden="1">
       <c r="A517" s="2" t="s">
         <v>973</v>
       </c>
@@ -43379,7 +43380,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="518" spans="1:18">
+    <row r="518" spans="1:18" hidden="1">
       <c r="A518" s="2" t="s">
         <v>975</v>
       </c>
@@ -43435,7 +43436,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="519" spans="1:18">
+    <row r="519" spans="1:18" hidden="1">
       <c r="A519" s="2" t="s">
         <v>977</v>
       </c>
@@ -43491,7 +43492,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="520" spans="1:18">
+    <row r="520" spans="1:18" hidden="1">
       <c r="A520" s="2" t="s">
         <v>979</v>
       </c>
@@ -43547,7 +43548,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="521" spans="1:18">
+    <row r="521" spans="1:18" hidden="1">
       <c r="A521" s="2" t="s">
         <v>981</v>
       </c>
@@ -43603,7 +43604,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="522" spans="1:18">
+    <row r="522" spans="1:18" hidden="1">
       <c r="A522" s="2" t="s">
         <v>983</v>
       </c>
@@ -43659,7 +43660,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="523" spans="1:18">
+    <row r="523" spans="1:18" hidden="1">
       <c r="A523" s="2" t="s">
         <v>985</v>
       </c>
@@ -43827,7 +43828,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="526" spans="1:18">
+    <row r="526" spans="1:18" hidden="1">
       <c r="A526" s="2" t="s">
         <v>991</v>
       </c>
@@ -43939,7 +43940,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="528" spans="1:18">
+    <row r="528" spans="1:18" hidden="1">
       <c r="A528" s="2" t="s">
         <v>995</v>
       </c>
@@ -43995,7 +43996,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="529" spans="1:18">
+    <row r="529" spans="1:18" hidden="1">
       <c r="A529" s="2" t="s">
         <v>997</v>
       </c>
@@ -44051,7 +44052,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="530" spans="1:18">
+    <row r="530" spans="1:18" hidden="1">
       <c r="A530" s="2" t="s">
         <v>999</v>
       </c>
@@ -44107,7 +44108,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="531" spans="1:18">
+    <row r="531" spans="1:18" hidden="1">
       <c r="A531" s="2" t="s">
         <v>999</v>
       </c>
@@ -44163,7 +44164,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="532" spans="1:18">
+    <row r="532" spans="1:18" hidden="1">
       <c r="A532" s="2" t="s">
         <v>1001</v>
       </c>
@@ -44219,7 +44220,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="533" spans="1:18">
+    <row r="533" spans="1:18" hidden="1">
       <c r="A533" s="2" t="s">
         <v>1003</v>
       </c>
@@ -44275,7 +44276,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="534" spans="1:18">
+    <row r="534" spans="1:18" hidden="1">
       <c r="A534" s="2" t="s">
         <v>1005</v>
       </c>
@@ -44331,7 +44332,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="535" spans="1:18">
+    <row r="535" spans="1:18" hidden="1">
       <c r="A535" s="2" t="s">
         <v>1007</v>
       </c>
@@ -44387,7 +44388,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="536" spans="1:18">
+    <row r="536" spans="1:18" hidden="1">
       <c r="A536" s="2" t="s">
         <v>1007</v>
       </c>
@@ -44443,7 +44444,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="537" spans="1:18">
+    <row r="537" spans="1:18" hidden="1">
       <c r="A537" s="2" t="s">
         <v>1009</v>
       </c>
@@ -44499,7 +44500,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="538" spans="1:18">
+    <row r="538" spans="1:18" hidden="1">
       <c r="A538" s="2" t="s">
         <v>1011</v>
       </c>
@@ -44555,7 +44556,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="539" spans="1:18">
+    <row r="539" spans="1:18" hidden="1">
       <c r="A539" s="2" t="s">
         <v>1013</v>
       </c>
@@ -44611,7 +44612,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="540" spans="1:18">
+    <row r="540" spans="1:18" hidden="1">
       <c r="A540" s="2" t="s">
         <v>1015</v>
       </c>
@@ -44667,7 +44668,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="541" spans="1:18">
+    <row r="541" spans="1:18" hidden="1">
       <c r="A541" s="2" t="s">
         <v>1017</v>
       </c>
@@ -44779,7 +44780,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="543" spans="1:18">
+    <row r="543" spans="1:18" hidden="1">
       <c r="A543" s="2" t="s">
         <v>1021</v>
       </c>
@@ -44835,7 +44836,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="544" spans="1:18">
+    <row r="544" spans="1:18" hidden="1">
       <c r="A544" s="2" t="s">
         <v>1021</v>
       </c>
@@ -44891,7 +44892,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="545" spans="1:18">
+    <row r="545" spans="1:18" hidden="1">
       <c r="A545" s="2" t="s">
         <v>1023</v>
       </c>
@@ -44947,7 +44948,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="546" spans="1:18">
+    <row r="546" spans="1:18" hidden="1">
       <c r="A546" s="2" t="s">
         <v>1025</v>
       </c>
@@ -45059,7 +45060,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="548" spans="1:18">
+    <row r="548" spans="1:18" hidden="1">
       <c r="A548" s="2" t="s">
         <v>1029</v>
       </c>
@@ -45115,7 +45116,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="549" spans="1:18">
+    <row r="549" spans="1:18" hidden="1">
       <c r="A549" s="2" t="s">
         <v>1031</v>
       </c>
@@ -45171,7 +45172,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="550" spans="1:18">
+    <row r="550" spans="1:18" hidden="1">
       <c r="A550" s="2" t="s">
         <v>1033</v>
       </c>
@@ -45227,7 +45228,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="551" spans="1:18">
+    <row r="551" spans="1:18" hidden="1">
       <c r="A551" s="2" t="s">
         <v>1035</v>
       </c>
@@ -45283,7 +45284,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="552" spans="1:18">
+    <row r="552" spans="1:18" hidden="1">
       <c r="A552" s="2" t="s">
         <v>1037</v>
       </c>
@@ -45339,7 +45340,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="553" spans="1:18">
+    <row r="553" spans="1:18" hidden="1">
       <c r="A553" s="2" t="s">
         <v>1039</v>
       </c>
@@ -45395,7 +45396,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="554" spans="1:18">
+    <row r="554" spans="1:18" hidden="1">
       <c r="A554" s="2" t="s">
         <v>1039</v>
       </c>
@@ -45451,7 +45452,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="555" spans="1:18">
+    <row r="555" spans="1:18" hidden="1">
       <c r="A555" s="2" t="s">
         <v>1041</v>
       </c>
@@ -45507,7 +45508,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="556" spans="1:18">
+    <row r="556" spans="1:18" hidden="1">
       <c r="A556" s="2" t="s">
         <v>1043</v>
       </c>
@@ -45619,7 +45620,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="558" spans="1:18">
+    <row r="558" spans="1:18" hidden="1">
       <c r="A558" s="2" t="s">
         <v>1047</v>
       </c>
@@ -45675,7 +45676,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="559" spans="1:18">
+    <row r="559" spans="1:18" hidden="1">
       <c r="A559" s="2" t="s">
         <v>1049</v>
       </c>
@@ -45731,7 +45732,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="560" spans="1:18">
+    <row r="560" spans="1:18" hidden="1">
       <c r="A560" s="2" t="s">
         <v>1049</v>
       </c>
@@ -45787,7 +45788,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="561" spans="1:18">
+    <row r="561" spans="1:18" hidden="1">
       <c r="A561" s="2" t="s">
         <v>1051</v>
       </c>
@@ -45843,7 +45844,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="562" spans="1:18">
+    <row r="562" spans="1:18" hidden="1">
       <c r="A562" s="2" t="s">
         <v>1051</v>
       </c>
@@ -45899,7 +45900,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="563" spans="1:18">
+    <row r="563" spans="1:18" hidden="1">
       <c r="A563" s="2" t="s">
         <v>1053</v>
       </c>
@@ -45955,7 +45956,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="564" spans="1:18">
+    <row r="564" spans="1:18" hidden="1">
       <c r="A564" s="2" t="s">
         <v>1055</v>
       </c>
@@ -46067,7 +46068,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="566" spans="1:18">
+    <row r="566" spans="1:18" hidden="1">
       <c r="A566" s="2" t="s">
         <v>1059</v>
       </c>
@@ -46235,7 +46236,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="569" spans="1:18">
+    <row r="569" spans="1:18" hidden="1">
       <c r="A569" s="2" t="s">
         <v>1065</v>
       </c>
@@ -46291,7 +46292,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="570" spans="1:18">
+    <row r="570" spans="1:18" hidden="1">
       <c r="A570" s="2" t="s">
         <v>1067</v>
       </c>
@@ -46347,7 +46348,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="571" spans="1:18">
+    <row r="571" spans="1:18" hidden="1">
       <c r="A571" s="2" t="s">
         <v>1069</v>
       </c>
@@ -46403,7 +46404,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="572" spans="1:18">
+    <row r="572" spans="1:18" hidden="1">
       <c r="A572" s="2" t="s">
         <v>1071</v>
       </c>
@@ -46459,7 +46460,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="573" spans="1:18">
+    <row r="573" spans="1:18" hidden="1">
       <c r="A573" s="2" t="s">
         <v>1073</v>
       </c>
@@ -46571,7 +46572,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="575" spans="1:18">
+    <row r="575" spans="1:18" hidden="1">
       <c r="A575" s="2" t="s">
         <v>1077</v>
       </c>
@@ -46627,7 +46628,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="576" spans="1:18">
+    <row r="576" spans="1:18" hidden="1">
       <c r="A576" s="2" t="s">
         <v>1077</v>
       </c>
@@ -46683,7 +46684,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="577" spans="1:18">
+    <row r="577" spans="1:18" hidden="1">
       <c r="A577" s="2" t="s">
         <v>1079</v>
       </c>
@@ -46851,7 +46852,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="580" spans="1:18">
+    <row r="580" spans="1:18" hidden="1">
       <c r="A580" s="2" t="s">
         <v>1085</v>
       </c>
@@ -46963,7 +46964,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="582" spans="1:18">
+    <row r="582" spans="1:18" hidden="1">
       <c r="A582" s="2" t="s">
         <v>1089</v>
       </c>
@@ -47019,7 +47020,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="583" spans="1:18">
+    <row r="583" spans="1:18" hidden="1">
       <c r="A583" s="2" t="s">
         <v>1091</v>
       </c>
@@ -47075,7 +47076,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="584" spans="1:18">
+    <row r="584" spans="1:18" hidden="1">
       <c r="A584" s="2" t="s">
         <v>1093</v>
       </c>
@@ -47131,7 +47132,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="585" spans="1:18">
+    <row r="585" spans="1:18" hidden="1">
       <c r="A585" s="2" t="s">
         <v>1095</v>
       </c>
@@ -47187,7 +47188,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="586" spans="1:18">
+    <row r="586" spans="1:18" hidden="1">
       <c r="A586" s="2" t="s">
         <v>1097</v>
       </c>
@@ -47243,7 +47244,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="587" spans="1:18">
+    <row r="587" spans="1:18" hidden="1">
       <c r="A587" s="2" t="s">
         <v>1099</v>
       </c>
@@ -47299,7 +47300,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="588" spans="1:18">
+    <row r="588" spans="1:18" hidden="1">
       <c r="A588" s="2" t="s">
         <v>1101</v>
       </c>
@@ -47355,7 +47356,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="589" spans="1:18">
+    <row r="589" spans="1:18" hidden="1">
       <c r="A589" s="2" t="s">
         <v>1103</v>
       </c>
@@ -47411,7 +47412,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="590" spans="1:18">
+    <row r="590" spans="1:18" hidden="1">
       <c r="A590" s="2" t="s">
         <v>1103</v>
       </c>
@@ -47467,7 +47468,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="591" spans="1:18">
+    <row r="591" spans="1:18" hidden="1">
       <c r="A591" s="2" t="s">
         <v>1105</v>
       </c>
@@ -47523,7 +47524,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="592" spans="1:18">
+    <row r="592" spans="1:18" hidden="1">
       <c r="A592" s="2" t="s">
         <v>1105</v>
       </c>
@@ -47579,7 +47580,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="593" spans="1:18">
+    <row r="593" spans="1:18" hidden="1">
       <c r="A593" s="2" t="s">
         <v>1107</v>
       </c>
@@ -47635,7 +47636,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="594" spans="1:18">
+    <row r="594" spans="1:18" hidden="1">
       <c r="A594" s="2" t="s">
         <v>1109</v>
       </c>
@@ -47691,7 +47692,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="595" spans="1:18">
+    <row r="595" spans="1:18" hidden="1">
       <c r="A595" s="2" t="s">
         <v>1111</v>
       </c>
@@ -47747,7 +47748,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="596" spans="1:18">
+    <row r="596" spans="1:18" hidden="1">
       <c r="A596" s="2" t="s">
         <v>1113</v>
       </c>
@@ -47803,7 +47804,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="597" spans="1:18">
+    <row r="597" spans="1:18" hidden="1">
       <c r="A597" s="2" t="s">
         <v>1115</v>
       </c>
@@ -47859,7 +47860,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="598" spans="1:18">
+    <row r="598" spans="1:18" hidden="1">
       <c r="A598" s="2" t="s">
         <v>1117</v>
       </c>
@@ -47915,7 +47916,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="599" spans="1:18">
+    <row r="599" spans="1:18" hidden="1">
       <c r="A599" s="2" t="s">
         <v>1119</v>
       </c>
@@ -47971,7 +47972,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="600" spans="1:18">
+    <row r="600" spans="1:18" hidden="1">
       <c r="A600" s="2" t="s">
         <v>1121</v>
       </c>
@@ -48027,7 +48028,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="601" spans="1:18">
+    <row r="601" spans="1:18" hidden="1">
       <c r="A601" s="2" t="s">
         <v>1123</v>
       </c>
@@ -48083,7 +48084,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="602" spans="1:18">
+    <row r="602" spans="1:18" hidden="1">
       <c r="A602" s="2" t="s">
         <v>1125</v>
       </c>
@@ -48139,7 +48140,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="603" spans="1:18">
+    <row r="603" spans="1:18" hidden="1">
       <c r="A603" s="2" t="s">
         <v>1127</v>
       </c>
@@ -48195,7 +48196,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="604" spans="1:18">
+    <row r="604" spans="1:18" hidden="1">
       <c r="A604" s="2" t="s">
         <v>1129</v>
       </c>
@@ -48251,7 +48252,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="605" spans="1:18">
+    <row r="605" spans="1:18" hidden="1">
       <c r="A605" s="2" t="s">
         <v>1131</v>
       </c>
@@ -48307,7 +48308,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="606" spans="1:18">
+    <row r="606" spans="1:18" hidden="1">
       <c r="A606" s="2" t="s">
         <v>1131</v>
       </c>
@@ -48363,7 +48364,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="607" spans="1:18">
+    <row r="607" spans="1:18" hidden="1">
       <c r="A607" s="2" t="s">
         <v>1133</v>
       </c>
@@ -48419,7 +48420,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="608" spans="1:18">
+    <row r="608" spans="1:18" hidden="1">
       <c r="A608" s="2" t="s">
         <v>1135</v>
       </c>
@@ -48475,7 +48476,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="609" spans="1:18">
+    <row r="609" spans="1:18" hidden="1">
       <c r="A609" s="2" t="s">
         <v>1137</v>
       </c>
@@ -48531,7 +48532,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="610" spans="1:18">
+    <row r="610" spans="1:18" hidden="1">
       <c r="A610" s="2" t="s">
         <v>1139</v>
       </c>
@@ -48587,7 +48588,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="611" spans="1:18">
+    <row r="611" spans="1:18" hidden="1">
       <c r="A611" s="2" t="s">
         <v>1141</v>
       </c>
@@ -48643,7 +48644,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="612" spans="1:18">
+    <row r="612" spans="1:18" hidden="1">
       <c r="A612" s="2" t="s">
         <v>1143</v>
       </c>
@@ -48699,7 +48700,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="613" spans="1:18">
+    <row r="613" spans="1:18" hidden="1">
       <c r="A613" s="2" t="s">
         <v>1145</v>
       </c>
@@ -48755,7 +48756,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="614" spans="1:18">
+    <row r="614" spans="1:18" hidden="1">
       <c r="A614" s="2" t="s">
         <v>1147</v>
       </c>
@@ -48867,7 +48868,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="616" spans="1:18">
+    <row r="616" spans="1:18" hidden="1">
       <c r="A616" s="2" t="s">
         <v>1151</v>
       </c>
@@ -48923,7 +48924,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="617" spans="1:18">
+    <row r="617" spans="1:18" hidden="1">
       <c r="A617" s="2" t="s">
         <v>1153</v>
       </c>
@@ -48979,7 +48980,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="618" spans="1:18">
+    <row r="618" spans="1:18" hidden="1">
       <c r="A618" s="2" t="s">
         <v>1155</v>
       </c>
@@ -49035,7 +49036,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="619" spans="1:18">
+    <row r="619" spans="1:18" hidden="1">
       <c r="A619" s="2" t="s">
         <v>1157</v>
       </c>
@@ -49091,7 +49092,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="620" spans="1:18">
+    <row r="620" spans="1:18" hidden="1">
       <c r="A620" s="2" t="s">
         <v>1157</v>
       </c>
@@ -49147,7 +49148,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="621" spans="1:18">
+    <row r="621" spans="1:18" hidden="1">
       <c r="A621" s="2" t="s">
         <v>1159</v>
       </c>
@@ -49203,7 +49204,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="622" spans="1:18">
+    <row r="622" spans="1:18" hidden="1">
       <c r="A622" s="2" t="s">
         <v>1161</v>
       </c>
@@ -49259,7 +49260,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="623" spans="1:18">
+    <row r="623" spans="1:18" hidden="1">
       <c r="A623" s="2" t="s">
         <v>1163</v>
       </c>
@@ -49315,7 +49316,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="624" spans="1:18">
+    <row r="624" spans="1:18" hidden="1">
       <c r="A624" s="2" t="s">
         <v>1165</v>
       </c>
@@ -49371,7 +49372,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="625" spans="1:18">
+    <row r="625" spans="1:18" hidden="1">
       <c r="A625" s="2" t="s">
         <v>1165</v>
       </c>
@@ -49427,7 +49428,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="626" spans="1:18">
+    <row r="626" spans="1:18" hidden="1">
       <c r="A626" s="2" t="s">
         <v>1167</v>
       </c>
@@ -49483,7 +49484,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="627" spans="1:18">
+    <row r="627" spans="1:18" hidden="1">
       <c r="A627" s="2" t="s">
         <v>1169</v>
       </c>
@@ -49539,7 +49540,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="628" spans="1:18">
+    <row r="628" spans="1:18" hidden="1">
       <c r="A628" s="2" t="s">
         <v>1169</v>
       </c>
@@ -49987,7 +49988,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="636" spans="1:18">
+    <row r="636" spans="1:18" hidden="1">
       <c r="A636" s="2" t="s">
         <v>1185</v>
       </c>
@@ -50043,7 +50044,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="637" spans="1:18">
+    <row r="637" spans="1:18" hidden="1">
       <c r="A637" s="2" t="s">
         <v>1187</v>
       </c>
@@ -50323,7 +50324,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="642" spans="1:18">
+    <row r="642" spans="1:18" hidden="1">
       <c r="A642" s="2" t="s">
         <v>1197</v>
       </c>
@@ -50379,7 +50380,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="643" spans="1:18">
+    <row r="643" spans="1:18" hidden="1">
       <c r="A643" s="2" t="s">
         <v>1199</v>
       </c>
@@ -50435,7 +50436,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="644" spans="1:18">
+    <row r="644" spans="1:18" hidden="1">
       <c r="A644" s="2" t="s">
         <v>1201</v>
       </c>
@@ -50491,7 +50492,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="645" spans="1:18">
+    <row r="645" spans="1:18" hidden="1">
       <c r="A645" s="2" t="s">
         <v>1203</v>
       </c>
@@ -50547,7 +50548,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="646" spans="1:18">
+    <row r="646" spans="1:18" hidden="1">
       <c r="A646" s="2" t="s">
         <v>1205</v>
       </c>
@@ -50603,7 +50604,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="647" spans="1:18">
+    <row r="647" spans="1:18" hidden="1">
       <c r="A647" s="2" t="s">
         <v>1207</v>
       </c>
@@ -50659,7 +50660,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="648" spans="1:18">
+    <row r="648" spans="1:18" hidden="1">
       <c r="A648" s="2" t="s">
         <v>1207</v>
       </c>
@@ -50715,7 +50716,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="649" spans="1:18">
+    <row r="649" spans="1:18" hidden="1">
       <c r="A649" s="2" t="s">
         <v>1209</v>
       </c>
@@ -50939,7 +50940,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="653" spans="1:18">
+    <row r="653" spans="1:18" hidden="1">
       <c r="A653" s="2" t="s">
         <v>1217</v>
       </c>
@@ -50995,7 +50996,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="654" spans="1:18">
+    <row r="654" spans="1:18" hidden="1">
       <c r="A654" s="2" t="s">
         <v>1219</v>
       </c>
@@ -51107,7 +51108,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="656" spans="1:18">
+    <row r="656" spans="1:18" hidden="1">
       <c r="A656" s="2" t="s">
         <v>1223</v>
       </c>
@@ -51275,7 +51276,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="659" spans="1:18">
+    <row r="659" spans="1:18" hidden="1">
       <c r="A659" s="2" t="s">
         <v>1229</v>
       </c>
@@ -51555,7 +51556,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="664" spans="1:18">
+    <row r="664" spans="1:18" hidden="1">
       <c r="A664" s="2" t="s">
         <v>1239</v>
       </c>
@@ -51891,7 +51892,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="670" spans="1:18">
+    <row r="670" spans="1:18" hidden="1">
       <c r="A670" s="2" t="s">
         <v>1251</v>
       </c>
@@ -51947,7 +51948,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="671" spans="1:18">
+    <row r="671" spans="1:18" hidden="1">
       <c r="A671" s="2" t="s">
         <v>1251</v>
       </c>
@@ -52059,7 +52060,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="673" spans="1:18">
+    <row r="673" spans="1:18" hidden="1">
       <c r="A673" s="2" t="s">
         <v>1255</v>
       </c>
@@ -52115,7 +52116,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="674" spans="1:18">
+    <row r="674" spans="1:18" hidden="1">
       <c r="A674" s="2" t="s">
         <v>1257</v>
       </c>
@@ -52227,7 +52228,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="676" spans="1:18">
+    <row r="676" spans="1:18" hidden="1">
       <c r="A676" s="2" t="s">
         <v>1261</v>
       </c>
@@ -52283,7 +52284,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="677" spans="1:18">
+    <row r="677" spans="1:18" hidden="1">
       <c r="A677" s="2" t="s">
         <v>1263</v>
       </c>
@@ -52339,7 +52340,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="678" spans="1:18">
+    <row r="678" spans="1:18" hidden="1">
       <c r="A678" s="2" t="s">
         <v>1265</v>
       </c>
@@ -52395,7 +52396,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="679" spans="1:18">
+    <row r="679" spans="1:18" hidden="1">
       <c r="A679" s="2" t="s">
         <v>1265</v>
       </c>
@@ -52451,7 +52452,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="680" spans="1:18">
+    <row r="680" spans="1:18" hidden="1">
       <c r="A680" s="2" t="s">
         <v>1265</v>
       </c>
@@ -52507,7 +52508,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="681" spans="1:18">
+    <row r="681" spans="1:18" hidden="1">
       <c r="A681" s="2" t="s">
         <v>1267</v>
       </c>
@@ -52563,7 +52564,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="682" spans="1:18">
+    <row r="682" spans="1:18" hidden="1">
       <c r="A682" s="2" t="s">
         <v>1269</v>
       </c>
@@ -52619,7 +52620,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="683" spans="1:18">
+    <row r="683" spans="1:18" hidden="1">
       <c r="A683" s="2" t="s">
         <v>1271</v>
       </c>
@@ -52675,7 +52676,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="684" spans="1:18">
+    <row r="684" spans="1:18" hidden="1">
       <c r="A684" s="2" t="s">
         <v>1273</v>
       </c>
@@ -52731,7 +52732,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="685" spans="1:18">
+    <row r="685" spans="1:18" hidden="1">
       <c r="A685" s="2" t="s">
         <v>1273</v>
       </c>
@@ -52843,7 +52844,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="687" spans="1:18">
+    <row r="687" spans="1:18" hidden="1">
       <c r="A687" s="2" t="s">
         <v>1277</v>
       </c>
@@ -52899,7 +52900,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="688" spans="1:18">
+    <row r="688" spans="1:18" hidden="1">
       <c r="A688" s="2" t="s">
         <v>1279</v>
       </c>
@@ -53011,7 +53012,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="690" spans="1:18">
+    <row r="690" spans="1:18" hidden="1">
       <c r="A690" s="2" t="s">
         <v>1283</v>
       </c>
@@ -53067,7 +53068,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="691" spans="1:18">
+    <row r="691" spans="1:18" hidden="1">
       <c r="A691" s="2" t="s">
         <v>1283</v>
       </c>
@@ -53123,7 +53124,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="692" spans="1:18">
+    <row r="692" spans="1:18" hidden="1">
       <c r="A692" s="2" t="s">
         <v>1283</v>
       </c>
@@ -53235,7 +53236,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="694" spans="1:18">
+    <row r="694" spans="1:18" hidden="1">
       <c r="A694" s="2" t="s">
         <v>1287</v>
       </c>
@@ -53291,7 +53292,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="695" spans="1:18">
+    <row r="695" spans="1:18" hidden="1">
       <c r="A695" s="2" t="s">
         <v>1289</v>
       </c>
@@ -53403,7 +53404,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="697" spans="1:18">
+    <row r="697" spans="1:18" hidden="1">
       <c r="A697" s="2" t="s">
         <v>1293</v>
       </c>
@@ -53459,7 +53460,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="698" spans="1:18">
+    <row r="698" spans="1:18" hidden="1">
       <c r="A698" s="2" t="s">
         <v>1295</v>
       </c>
@@ -53571,7 +53572,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="700" spans="1:18">
+    <row r="700" spans="1:18" hidden="1">
       <c r="A700" s="2" t="s">
         <v>1299</v>
       </c>
@@ -53627,7 +53628,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="701" spans="1:18">
+    <row r="701" spans="1:18" hidden="1">
       <c r="A701" s="2" t="s">
         <v>1301</v>
       </c>
@@ -53739,7 +53740,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="703" spans="1:18">
+    <row r="703" spans="1:18" hidden="1">
       <c r="A703" s="2" t="s">
         <v>1305</v>
       </c>
@@ -53795,7 +53796,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="704" spans="1:18">
+    <row r="704" spans="1:18" hidden="1">
       <c r="A704" s="2" t="s">
         <v>1307</v>
       </c>
@@ -53851,7 +53852,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="705" spans="1:18">
+    <row r="705" spans="1:18" hidden="1">
       <c r="A705" s="2" t="s">
         <v>1309</v>
       </c>
@@ -53907,7 +53908,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="706" spans="1:18">
+    <row r="706" spans="1:18" hidden="1">
       <c r="A706" s="2" t="s">
         <v>1311</v>
       </c>
@@ -53963,7 +53964,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="707" spans="1:18">
+    <row r="707" spans="1:18" hidden="1">
       <c r="A707" s="2" t="s">
         <v>1313</v>
       </c>
@@ -54019,7 +54020,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="708" spans="1:18">
+    <row r="708" spans="1:18" hidden="1">
       <c r="A708" s="2" t="s">
         <v>1315</v>
       </c>
@@ -54075,7 +54076,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="709" spans="1:18">
+    <row r="709" spans="1:18" hidden="1">
       <c r="A709" s="2" t="s">
         <v>1317</v>
       </c>
@@ -54131,7 +54132,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="710" spans="1:18">
+    <row r="710" spans="1:18" hidden="1">
       <c r="A710" s="2" t="s">
         <v>1319</v>
       </c>
@@ -54299,7 +54300,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="713" spans="1:18">
+    <row r="713" spans="1:18" hidden="1">
       <c r="A713" s="2" t="s">
         <v>1325</v>
       </c>
@@ -54355,7 +54356,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="714" spans="1:18">
+    <row r="714" spans="1:18" hidden="1">
       <c r="A714" s="2" t="s">
         <v>1327</v>
       </c>
@@ -54411,7 +54412,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="715" spans="1:18">
+    <row r="715" spans="1:18" hidden="1">
       <c r="A715" s="2" t="s">
         <v>1327</v>
       </c>
@@ -54523,7 +54524,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="717" spans="1:18">
+    <row r="717" spans="1:18" hidden="1">
       <c r="A717" s="2" t="s">
         <v>1331</v>
       </c>
@@ -54579,7 +54580,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="718" spans="1:18">
+    <row r="718" spans="1:18" hidden="1">
       <c r="A718" s="2" t="s">
         <v>1331</v>
       </c>
@@ -54635,7 +54636,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="719" spans="1:18">
+    <row r="719" spans="1:18" hidden="1">
       <c r="A719" s="2" t="s">
         <v>1333</v>
       </c>
@@ -54691,7 +54692,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="720" spans="1:18">
+    <row r="720" spans="1:18" hidden="1">
       <c r="A720" s="2" t="s">
         <v>1333</v>
       </c>
@@ -54747,7 +54748,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="721" spans="1:18">
+    <row r="721" spans="1:18" hidden="1">
       <c r="A721" s="2" t="s">
         <v>1335</v>
       </c>
@@ -54803,7 +54804,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="722" spans="1:18">
+    <row r="722" spans="1:18" hidden="1">
       <c r="A722" s="2" t="s">
         <v>1337</v>
       </c>
@@ -54859,7 +54860,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="723" spans="1:18">
+    <row r="723" spans="1:18" hidden="1">
       <c r="A723" s="2" t="s">
         <v>1339</v>
       </c>
@@ -54915,7 +54916,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="724" spans="1:18">
+    <row r="724" spans="1:18" hidden="1">
       <c r="A724" s="2" t="s">
         <v>1341</v>
       </c>
@@ -55027,7 +55028,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="726" spans="1:18">
+    <row r="726" spans="1:18" hidden="1">
       <c r="A726" s="2" t="s">
         <v>1345</v>
       </c>
@@ -55139,7 +55140,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="728" spans="1:18">
+    <row r="728" spans="1:18" hidden="1">
       <c r="A728" s="2" t="s">
         <v>1349</v>
       </c>
@@ -55251,7 +55252,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="730" spans="1:18">
+    <row r="730" spans="1:18" hidden="1">
       <c r="A730" s="2" t="s">
         <v>1353</v>
       </c>
@@ -55307,7 +55308,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="731" spans="1:18">
+    <row r="731" spans="1:18" hidden="1">
       <c r="A731" s="2" t="s">
         <v>1355</v>
       </c>
@@ -55363,7 +55364,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="732" spans="1:18">
+    <row r="732" spans="1:18" hidden="1">
       <c r="A732" s="2" t="s">
         <v>1357</v>
       </c>
@@ -55419,7 +55420,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="733" spans="1:18">
+    <row r="733" spans="1:18" hidden="1">
       <c r="A733" s="2" t="s">
         <v>1359</v>
       </c>
@@ -55475,7 +55476,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="734" spans="1:18">
+    <row r="734" spans="1:18" hidden="1">
       <c r="A734" s="2" t="s">
         <v>1361</v>
       </c>
@@ -55531,7 +55532,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="735" spans="1:18">
+    <row r="735" spans="1:18" hidden="1">
       <c r="A735" s="2" t="s">
         <v>1363</v>
       </c>
@@ -55587,7 +55588,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="736" spans="1:18">
+    <row r="736" spans="1:18" hidden="1">
       <c r="A736" s="2" t="s">
         <v>1365</v>
       </c>
@@ -55643,7 +55644,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="737" spans="1:18">
+    <row r="737" spans="1:18" hidden="1">
       <c r="A737" s="2" t="s">
         <v>1367</v>
       </c>
@@ -55699,7 +55700,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="738" spans="1:18">
+    <row r="738" spans="1:18" hidden="1">
       <c r="A738" s="2" t="s">
         <v>1369</v>
       </c>
@@ -55755,7 +55756,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="739" spans="1:18">
+    <row r="739" spans="1:18" hidden="1">
       <c r="A739" s="2" t="s">
         <v>1371</v>
       </c>
@@ -55811,7 +55812,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="740" spans="1:18">
+    <row r="740" spans="1:18" hidden="1">
       <c r="A740" s="2" t="s">
         <v>1373</v>
       </c>
@@ -55867,7 +55868,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="741" spans="1:18">
+    <row r="741" spans="1:18" hidden="1">
       <c r="A741" s="2" t="s">
         <v>1373</v>
       </c>
@@ -55923,7 +55924,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="742" spans="1:18">
+    <row r="742" spans="1:18" hidden="1">
       <c r="A742" s="2" t="s">
         <v>1375</v>
       </c>
@@ -55979,7 +55980,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="743" spans="1:18">
+    <row r="743" spans="1:18" hidden="1">
       <c r="A743" s="2" t="s">
         <v>1377</v>
       </c>
@@ -56035,7 +56036,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="744" spans="1:18">
+    <row r="744" spans="1:18" hidden="1">
       <c r="A744" s="2" t="s">
         <v>1379</v>
       </c>
@@ -56147,7 +56148,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="746" spans="1:18">
+    <row r="746" spans="1:18" hidden="1">
       <c r="A746" s="2" t="s">
         <v>1383</v>
       </c>
@@ -56203,7 +56204,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="747" spans="1:18">
+    <row r="747" spans="1:18" hidden="1">
       <c r="A747" s="2" t="s">
         <v>1385</v>
       </c>
@@ -56259,7 +56260,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="748" spans="1:18">
+    <row r="748" spans="1:18" hidden="1">
       <c r="A748" s="2" t="s">
         <v>1387</v>
       </c>
@@ -56315,7 +56316,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="749" spans="1:18">
+    <row r="749" spans="1:18" hidden="1">
       <c r="A749" s="2" t="s">
         <v>1389</v>
       </c>
@@ -56371,7 +56372,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="750" spans="1:18">
+    <row r="750" spans="1:18" hidden="1">
       <c r="A750" s="2" t="s">
         <v>1391</v>
       </c>
@@ -56427,7 +56428,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="751" spans="1:18">
+    <row r="751" spans="1:18" hidden="1">
       <c r="A751" s="2" t="s">
         <v>1393</v>
       </c>
@@ -56483,7 +56484,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="752" spans="1:18">
+    <row r="752" spans="1:18" hidden="1">
       <c r="A752" s="2" t="s">
         <v>1395</v>
       </c>
@@ -56539,7 +56540,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="753" spans="1:18">
+    <row r="753" spans="1:18" hidden="1">
       <c r="A753" s="2" t="s">
         <v>1397</v>
       </c>
@@ -56595,7 +56596,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="754" spans="1:18">
+    <row r="754" spans="1:18" hidden="1">
       <c r="A754" s="2" t="s">
         <v>1399</v>
       </c>
@@ -56651,7 +56652,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="755" spans="1:18">
+    <row r="755" spans="1:18" hidden="1">
       <c r="A755" s="2" t="s">
         <v>1401</v>
       </c>
@@ -56707,7 +56708,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="756" spans="1:18">
+    <row r="756" spans="1:18" hidden="1">
       <c r="A756" s="2" t="s">
         <v>1403</v>
       </c>
@@ -56763,7 +56764,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="757" spans="1:18">
+    <row r="757" spans="1:18" hidden="1">
       <c r="A757" s="2" t="s">
         <v>1403</v>
       </c>
@@ -56819,7 +56820,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="758" spans="1:18">
+    <row r="758" spans="1:18" hidden="1">
       <c r="A758" s="2" t="s">
         <v>1405</v>
       </c>
@@ -56931,7 +56932,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="760" spans="1:18">
+    <row r="760" spans="1:18" hidden="1">
       <c r="A760" s="2" t="s">
         <v>1409</v>
       </c>
@@ -56987,7 +56988,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="761" spans="1:18">
+    <row r="761" spans="1:18" hidden="1">
       <c r="A761" s="2" t="s">
         <v>1411</v>
       </c>
@@ -57043,7 +57044,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="762" spans="1:18">
+    <row r="762" spans="1:18" hidden="1">
       <c r="A762" s="2" t="s">
         <v>1413</v>
       </c>
@@ -57099,7 +57100,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="763" spans="1:18">
+    <row r="763" spans="1:18" hidden="1">
       <c r="A763" s="2" t="s">
         <v>1415</v>
       </c>
@@ -57155,7 +57156,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="764" spans="1:18">
+    <row r="764" spans="1:18" hidden="1">
       <c r="A764" s="2" t="s">
         <v>1417</v>
       </c>
@@ -57211,7 +57212,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="765" spans="1:18">
+    <row r="765" spans="1:18" hidden="1">
       <c r="A765" s="2" t="s">
         <v>1419</v>
       </c>
@@ -57323,7 +57324,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="767" spans="1:18">
+    <row r="767" spans="1:18" hidden="1">
       <c r="A767" s="2" t="s">
         <v>1423</v>
       </c>
@@ -57379,7 +57380,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="768" spans="1:18">
+    <row r="768" spans="1:18" hidden="1">
       <c r="A768" s="2" t="s">
         <v>1425</v>
       </c>
@@ -57435,7 +57436,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="769" spans="1:18">
+    <row r="769" spans="1:18" hidden="1">
       <c r="A769" s="2" t="s">
         <v>1425</v>
       </c>
@@ -57491,7 +57492,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="770" spans="1:18">
+    <row r="770" spans="1:18" hidden="1">
       <c r="A770" s="2" t="s">
         <v>1427</v>
       </c>
@@ -57547,7 +57548,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="771" spans="1:18">
+    <row r="771" spans="1:18" hidden="1">
       <c r="A771" s="2" t="s">
         <v>1429</v>
       </c>
@@ -57603,7 +57604,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="772" spans="1:18">
+    <row r="772" spans="1:18" hidden="1">
       <c r="A772" s="2" t="s">
         <v>1431</v>
       </c>
@@ -57659,7 +57660,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="773" spans="1:18">
+    <row r="773" spans="1:18" hidden="1">
       <c r="A773" s="2" t="s">
         <v>1433</v>
       </c>
@@ -57715,7 +57716,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="774" spans="1:18">
+    <row r="774" spans="1:18" hidden="1">
       <c r="A774" s="2" t="s">
         <v>1435</v>
       </c>
@@ -57771,7 +57772,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="775" spans="1:18">
+    <row r="775" spans="1:18" hidden="1">
       <c r="A775" s="2" t="s">
         <v>1437</v>
       </c>
@@ -57827,7 +57828,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="776" spans="1:18">
+    <row r="776" spans="1:18" hidden="1">
       <c r="A776" s="2" t="s">
         <v>1439</v>
       </c>
@@ -57939,7 +57940,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="778" spans="1:18">
+    <row r="778" spans="1:18" hidden="1">
       <c r="A778" s="2" t="s">
         <v>1443</v>
       </c>
@@ -57995,7 +57996,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="779" spans="1:18">
+    <row r="779" spans="1:18" hidden="1">
       <c r="A779" s="2" t="s">
         <v>1445</v>
       </c>
@@ -58051,7 +58052,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="780" spans="1:18">
+    <row r="780" spans="1:18" hidden="1">
       <c r="A780" s="2" t="s">
         <v>1447</v>
       </c>
@@ -58107,7 +58108,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="781" spans="1:18">
+    <row r="781" spans="1:18" hidden="1">
       <c r="A781" s="2" t="s">
         <v>1449</v>
       </c>
@@ -58163,7 +58164,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="782" spans="1:18">
+    <row r="782" spans="1:18" hidden="1">
       <c r="A782" s="2" t="s">
         <v>1449</v>
       </c>
@@ -58219,7 +58220,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="783" spans="1:18">
+    <row r="783" spans="1:18" hidden="1">
       <c r="A783" s="2" t="s">
         <v>1451</v>
       </c>
@@ -58275,7 +58276,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="784" spans="1:18">
+    <row r="784" spans="1:18" hidden="1">
       <c r="A784" s="2" t="s">
         <v>1453</v>
       </c>
@@ -58331,7 +58332,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="785" spans="1:18">
+    <row r="785" spans="1:18" hidden="1">
       <c r="A785" s="2" t="s">
         <v>1455</v>
       </c>
@@ -58387,7 +58388,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="786" spans="1:18">
+    <row r="786" spans="1:18" hidden="1">
       <c r="A786" s="2" t="s">
         <v>1457</v>
       </c>
@@ -58443,7 +58444,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="787" spans="1:18">
+    <row r="787" spans="1:18" hidden="1">
       <c r="A787" s="2" t="s">
         <v>1457</v>
       </c>
@@ -58499,7 +58500,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="788" spans="1:18">
+    <row r="788" spans="1:18" hidden="1">
       <c r="A788" s="2" t="s">
         <v>1459</v>
       </c>
@@ -58555,7 +58556,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="789" spans="1:18">
+    <row r="789" spans="1:18" hidden="1">
       <c r="A789" s="2" t="s">
         <v>1461</v>
       </c>
@@ -58611,7 +58612,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="790" spans="1:18">
+    <row r="790" spans="1:18" hidden="1">
       <c r="A790" s="2" t="s">
         <v>1461</v>
       </c>
@@ -58723,7 +58724,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="792" spans="1:18">
+    <row r="792" spans="1:18" hidden="1">
       <c r="A792" s="2" t="s">
         <v>1465</v>
       </c>
@@ -58779,7 +58780,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="793" spans="1:18">
+    <row r="793" spans="1:18" hidden="1">
       <c r="A793" s="2" t="s">
         <v>1467</v>
       </c>
@@ -58835,7 +58836,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="794" spans="1:18">
+    <row r="794" spans="1:18" hidden="1">
       <c r="A794" s="2" t="s">
         <v>1469</v>
       </c>
@@ -58891,7 +58892,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="795" spans="1:18">
+    <row r="795" spans="1:18" hidden="1">
       <c r="A795" s="2" t="s">
         <v>1469</v>
       </c>
@@ -58947,7 +58948,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="796" spans="1:18">
+    <row r="796" spans="1:18" hidden="1">
       <c r="A796" s="2" t="s">
         <v>1471</v>
       </c>
@@ -59003,7 +59004,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="797" spans="1:18">
+    <row r="797" spans="1:18" hidden="1">
       <c r="A797" s="2" t="s">
         <v>1473</v>
       </c>
@@ -59059,7 +59060,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="798" spans="1:18">
+    <row r="798" spans="1:18" hidden="1">
       <c r="A798" s="2" t="s">
         <v>1475</v>
       </c>
@@ -59115,7 +59116,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="799" spans="1:18">
+    <row r="799" spans="1:18" hidden="1">
       <c r="A799" s="2" t="s">
         <v>1477</v>
       </c>
@@ -59227,7 +59228,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="801" spans="1:18">
+    <row r="801" spans="1:18" hidden="1">
       <c r="A801" s="2" t="s">
         <v>1481</v>
       </c>
@@ -59283,7 +59284,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="802" spans="1:18">
+    <row r="802" spans="1:18" hidden="1">
       <c r="A802" s="2" t="s">
         <v>1483</v>
       </c>
@@ -59339,7 +59340,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="803" spans="1:18">
+    <row r="803" spans="1:18" hidden="1">
       <c r="A803" s="2" t="s">
         <v>1483</v>
       </c>
@@ -59507,7 +59508,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="806" spans="1:18">
+    <row r="806" spans="1:18" hidden="1">
       <c r="A806" s="2" t="s">
         <v>1489</v>
       </c>
@@ -59563,7 +59564,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="807" spans="1:18">
+    <row r="807" spans="1:18" hidden="1">
       <c r="A807" s="2" t="s">
         <v>1491</v>
       </c>
@@ -59619,7 +59620,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="808" spans="1:18">
+    <row r="808" spans="1:18" hidden="1">
       <c r="A808" s="2" t="s">
         <v>1493</v>
       </c>
@@ -59731,7 +59732,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="810" spans="1:18">
+    <row r="810" spans="1:18" hidden="1">
       <c r="A810" s="2" t="s">
         <v>1497</v>
       </c>
@@ -59787,7 +59788,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="811" spans="1:18">
+    <row r="811" spans="1:18" hidden="1">
       <c r="A811" s="2" t="s">
         <v>1499</v>
       </c>
@@ -59843,7 +59844,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="812" spans="1:18">
+    <row r="812" spans="1:18" hidden="1">
       <c r="A812" s="2" t="s">
         <v>1501</v>
       </c>
@@ -59899,7 +59900,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="813" spans="1:18">
+    <row r="813" spans="1:18" hidden="1">
       <c r="A813" s="2" t="s">
         <v>1503</v>
       </c>
@@ -59955,7 +59956,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="814" spans="1:18">
+    <row r="814" spans="1:18" hidden="1">
       <c r="A814" s="2" t="s">
         <v>1505</v>
       </c>
@@ -60011,7 +60012,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="815" spans="1:18">
+    <row r="815" spans="1:18" hidden="1">
       <c r="A815" s="2" t="s">
         <v>1507</v>
       </c>
@@ -60067,7 +60068,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="816" spans="1:18">
+    <row r="816" spans="1:18" hidden="1">
       <c r="A816" s="2" t="s">
         <v>1507</v>
       </c>
@@ -60123,7 +60124,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="817" spans="1:18">
+    <row r="817" spans="1:18" hidden="1">
       <c r="A817" s="2" t="s">
         <v>1509</v>
       </c>
@@ -60179,7 +60180,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="818" spans="1:18">
+    <row r="818" spans="1:18" hidden="1">
       <c r="A818" s="2" t="s">
         <v>1511</v>
       </c>
@@ -60235,7 +60236,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="819" spans="1:18">
+    <row r="819" spans="1:18" hidden="1">
       <c r="A819" s="2" t="s">
         <v>1513</v>
       </c>
@@ -60291,7 +60292,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="820" spans="1:18">
+    <row r="820" spans="1:18" hidden="1">
       <c r="A820" s="2" t="s">
         <v>1515</v>
       </c>
@@ -60347,7 +60348,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="821" spans="1:18">
+    <row r="821" spans="1:18" hidden="1">
       <c r="A821" s="2" t="s">
         <v>1515</v>
       </c>
@@ -60403,7 +60404,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="822" spans="1:18">
+    <row r="822" spans="1:18" hidden="1">
       <c r="A822" s="2" t="s">
         <v>1517</v>
       </c>
@@ -60459,7 +60460,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="823" spans="1:18">
+    <row r="823" spans="1:18" hidden="1">
       <c r="A823" s="2" t="s">
         <v>1519</v>
       </c>
@@ -60515,7 +60516,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="824" spans="1:18">
+    <row r="824" spans="1:18" hidden="1">
       <c r="A824" s="2" t="s">
         <v>1521</v>
       </c>
@@ -60571,7 +60572,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="825" spans="1:18">
+    <row r="825" spans="1:18" hidden="1">
       <c r="A825" s="2" t="s">
         <v>1521</v>
       </c>
@@ -60627,7 +60628,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="826" spans="1:18">
+    <row r="826" spans="1:18" hidden="1">
       <c r="A826" s="2" t="s">
         <v>1523</v>
       </c>
@@ -60683,7 +60684,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="827" spans="1:18">
+    <row r="827" spans="1:18" hidden="1">
       <c r="A827" s="2" t="s">
         <v>1525</v>
       </c>
@@ -60739,7 +60740,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="828" spans="1:18">
+    <row r="828" spans="1:18" hidden="1">
       <c r="A828" s="2" t="s">
         <v>1527</v>
       </c>
@@ -60795,7 +60796,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="829" spans="1:18">
+    <row r="829" spans="1:18" hidden="1">
       <c r="A829" s="2" t="s">
         <v>1529</v>
       </c>
@@ -60851,7 +60852,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="830" spans="1:18">
+    <row r="830" spans="1:18" hidden="1">
       <c r="A830" s="2" t="s">
         <v>1531</v>
       </c>
@@ -60907,7 +60908,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="831" spans="1:18">
+    <row r="831" spans="1:18" hidden="1">
       <c r="A831" s="2" t="s">
         <v>1533</v>
       </c>
@@ -60963,7 +60964,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="832" spans="1:18">
+    <row r="832" spans="1:18" hidden="1">
       <c r="A832" s="2" t="s">
         <v>1533</v>
       </c>
@@ -61075,7 +61076,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="834" spans="1:18">
+    <row r="834" spans="1:18" hidden="1">
       <c r="A834" s="2" t="s">
         <v>1537</v>
       </c>
@@ -61131,7 +61132,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="835" spans="1:18">
+    <row r="835" spans="1:18" hidden="1">
       <c r="A835" s="2" t="s">
         <v>1539</v>
       </c>
@@ -61187,7 +61188,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="836" spans="1:18">
+    <row r="836" spans="1:18" hidden="1">
       <c r="A836" s="2" t="s">
         <v>1541</v>
       </c>
@@ -61243,7 +61244,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="837" spans="1:18">
+    <row r="837" spans="1:18" hidden="1">
       <c r="A837" s="2" t="s">
         <v>1543</v>
       </c>
@@ -61299,7 +61300,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="838" spans="1:18">
+    <row r="838" spans="1:18" hidden="1">
       <c r="A838" s="2" t="s">
         <v>1545</v>
       </c>
@@ -61355,7 +61356,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="839" spans="1:18">
+    <row r="839" spans="1:18" hidden="1">
       <c r="A839" s="2" t="s">
         <v>1547</v>
       </c>
@@ -61411,7 +61412,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="840" spans="1:18">
+    <row r="840" spans="1:18" hidden="1">
       <c r="A840" s="2" t="s">
         <v>1549</v>
       </c>
@@ -61467,7 +61468,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="841" spans="1:18">
+    <row r="841" spans="1:18" hidden="1">
       <c r="A841" s="2" t="s">
         <v>1551</v>
       </c>
@@ -61523,7 +61524,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="842" spans="1:18">
+    <row r="842" spans="1:18" hidden="1">
       <c r="A842" s="2" t="s">
         <v>1553</v>
       </c>
@@ -61579,7 +61580,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="843" spans="1:18">
+    <row r="843" spans="1:18" hidden="1">
       <c r="A843" s="2" t="s">
         <v>1553</v>
       </c>
@@ -61635,7 +61636,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="844" spans="1:18">
+    <row r="844" spans="1:18" hidden="1">
       <c r="A844" s="2" t="s">
         <v>1555</v>
       </c>
@@ -61691,7 +61692,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="845" spans="1:18">
+    <row r="845" spans="1:18" hidden="1">
       <c r="A845" s="2" t="s">
         <v>1555</v>
       </c>
@@ -61747,7 +61748,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="846" spans="1:18">
+    <row r="846" spans="1:18" hidden="1">
       <c r="A846" s="2" t="s">
         <v>1557</v>
       </c>
@@ -61803,7 +61804,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="847" spans="1:18">
+    <row r="847" spans="1:18" hidden="1">
       <c r="A847" s="2" t="s">
         <v>1557</v>
       </c>
@@ -61859,7 +61860,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="848" spans="1:18">
+    <row r="848" spans="1:18" hidden="1">
       <c r="A848" s="2" t="s">
         <v>1559</v>
       </c>
@@ -61971,7 +61972,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="850" spans="1:18">
+    <row r="850" spans="1:18" hidden="1">
       <c r="A850" s="2" t="s">
         <v>1563</v>
       </c>
@@ -62027,7 +62028,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="851" spans="1:18">
+    <row r="851" spans="1:18" hidden="1">
       <c r="A851" s="2" t="s">
         <v>1565</v>
       </c>
@@ -62083,7 +62084,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="852" spans="1:18">
+    <row r="852" spans="1:18" hidden="1">
       <c r="A852" s="2" t="s">
         <v>1565</v>
       </c>
@@ -62139,7 +62140,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="853" spans="1:18">
+    <row r="853" spans="1:18" hidden="1">
       <c r="A853" s="2" t="s">
         <v>1567</v>
       </c>
@@ -62195,7 +62196,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="854" spans="1:18">
+    <row r="854" spans="1:18" hidden="1">
       <c r="A854" s="2" t="s">
         <v>1569</v>
       </c>
@@ -62251,7 +62252,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="855" spans="1:18">
+    <row r="855" spans="1:18" hidden="1">
       <c r="A855" s="2" t="s">
         <v>1571</v>
       </c>
@@ -62307,7 +62308,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="856" spans="1:18">
+    <row r="856" spans="1:18" hidden="1">
       <c r="A856" s="2" t="s">
         <v>1573</v>
       </c>
@@ -62363,7 +62364,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="857" spans="1:18">
+    <row r="857" spans="1:18" hidden="1">
       <c r="A857" s="2" t="s">
         <v>1575</v>
       </c>
@@ -62419,7 +62420,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="858" spans="1:18">
+    <row r="858" spans="1:18" hidden="1">
       <c r="A858" s="2" t="s">
         <v>1577</v>
       </c>
@@ -62475,7 +62476,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="859" spans="1:18">
+    <row r="859" spans="1:18" hidden="1">
       <c r="A859" s="2" t="s">
         <v>1579</v>
       </c>
@@ -62531,7 +62532,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="860" spans="1:18">
+    <row r="860" spans="1:18" hidden="1">
       <c r="A860" s="2" t="s">
         <v>1579</v>
       </c>
@@ -62587,7 +62588,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="861" spans="1:18">
+    <row r="861" spans="1:18" hidden="1">
       <c r="A861" s="2" t="s">
         <v>1581</v>
       </c>
@@ -62755,7 +62756,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="864" spans="1:18">
+    <row r="864" spans="1:18" hidden="1">
       <c r="A864" s="2" t="s">
         <v>1587</v>
       </c>
@@ -62867,7 +62868,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="866" spans="1:18">
+    <row r="866" spans="1:18" hidden="1">
       <c r="A866" s="2" t="s">
         <v>1591</v>
       </c>
@@ -62923,7 +62924,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="867" spans="1:18">
+    <row r="867" spans="1:18" hidden="1">
       <c r="A867" s="2" t="s">
         <v>1593</v>
       </c>
@@ -62979,7 +62980,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="868" spans="1:18">
+    <row r="868" spans="1:18" hidden="1">
       <c r="A868" s="2" t="s">
         <v>1595</v>
       </c>
@@ -63035,7 +63036,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="869" spans="1:18">
+    <row r="869" spans="1:18" hidden="1">
       <c r="A869" s="2" t="s">
         <v>1597</v>
       </c>
@@ -63091,7 +63092,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="870" spans="1:18">
+    <row r="870" spans="1:18" hidden="1">
       <c r="A870" s="2" t="s">
         <v>1599</v>
       </c>
@@ -63147,7 +63148,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="871" spans="1:18">
+    <row r="871" spans="1:18" hidden="1">
       <c r="A871" s="2" t="s">
         <v>1599</v>
       </c>
@@ -63203,7 +63204,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="872" spans="1:18">
+    <row r="872" spans="1:18" hidden="1">
       <c r="A872" s="2" t="s">
         <v>1601</v>
       </c>
@@ -63259,7 +63260,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="873" spans="1:18">
+    <row r="873" spans="1:18" hidden="1">
       <c r="A873" s="2" t="s">
         <v>1603</v>
       </c>
@@ -63315,7 +63316,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="874" spans="1:18">
+    <row r="874" spans="1:18" hidden="1">
       <c r="A874" s="2" t="s">
         <v>1605</v>
       </c>
@@ -63371,7 +63372,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="875" spans="1:18">
+    <row r="875" spans="1:18" hidden="1">
       <c r="A875" s="2" t="s">
         <v>1607</v>
       </c>
@@ -63427,7 +63428,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="876" spans="1:18">
+    <row r="876" spans="1:18" hidden="1">
       <c r="A876" s="2" t="s">
         <v>1609</v>
       </c>
@@ -63483,7 +63484,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="877" spans="1:18">
+    <row r="877" spans="1:18" hidden="1">
       <c r="A877" s="2" t="s">
         <v>1611</v>
       </c>
@@ -63539,7 +63540,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="878" spans="1:18">
+    <row r="878" spans="1:18" hidden="1">
       <c r="A878" s="2" t="s">
         <v>1613</v>
       </c>
@@ -63595,7 +63596,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="879" spans="1:18">
+    <row r="879" spans="1:18" hidden="1">
       <c r="A879" s="2" t="s">
         <v>1615</v>
       </c>
@@ -63651,7 +63652,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="880" spans="1:18">
+    <row r="880" spans="1:18" hidden="1">
       <c r="A880" s="2" t="s">
         <v>1617</v>
       </c>
@@ -63707,7 +63708,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="881" spans="1:18">
+    <row r="881" spans="1:18" hidden="1">
       <c r="A881" s="2" t="s">
         <v>1619</v>
       </c>
@@ -63763,7 +63764,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="882" spans="1:18">
+    <row r="882" spans="1:18" hidden="1">
       <c r="A882" s="2" t="s">
         <v>1621</v>
       </c>
@@ -63819,7 +63820,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="883" spans="1:18">
+    <row r="883" spans="1:18" hidden="1">
       <c r="A883" s="2" t="s">
         <v>1623</v>
       </c>
@@ -63875,7 +63876,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="884" spans="1:18">
+    <row r="884" spans="1:18" hidden="1">
       <c r="A884" s="2" t="s">
         <v>1625</v>
       </c>
@@ -63931,7 +63932,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="885" spans="1:18">
+    <row r="885" spans="1:18" hidden="1">
       <c r="A885" s="2" t="s">
         <v>1627</v>
       </c>
@@ -63987,7 +63988,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="886" spans="1:18">
+    <row r="886" spans="1:18" hidden="1">
       <c r="A886" s="2" t="s">
         <v>1627</v>
       </c>
@@ -64043,7 +64044,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="887" spans="1:18">
+    <row r="887" spans="1:18" hidden="1">
       <c r="A887" s="2" t="s">
         <v>1629</v>
       </c>
@@ -64099,7 +64100,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="888" spans="1:18">
+    <row r="888" spans="1:18" hidden="1">
       <c r="A888" s="2" t="s">
         <v>1631</v>
       </c>
@@ -64155,7 +64156,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="889" spans="1:18">
+    <row r="889" spans="1:18" hidden="1">
       <c r="A889" s="2" t="s">
         <v>1633</v>
       </c>
@@ -64211,7 +64212,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="890" spans="1:18">
+    <row r="890" spans="1:18" hidden="1">
       <c r="A890" s="2" t="s">
         <v>1635</v>
       </c>
@@ -64267,7 +64268,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="891" spans="1:18">
+    <row r="891" spans="1:18" hidden="1">
       <c r="A891" s="2" t="s">
         <v>1635</v>
       </c>
@@ -64323,7 +64324,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="892" spans="1:18">
+    <row r="892" spans="1:18" hidden="1">
       <c r="A892" s="2" t="s">
         <v>1637</v>
       </c>
@@ -64379,7 +64380,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="893" spans="1:18">
+    <row r="893" spans="1:18" hidden="1">
       <c r="A893" s="2" t="s">
         <v>1639</v>
       </c>
@@ -64435,7 +64436,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="894" spans="1:18">
+    <row r="894" spans="1:18" hidden="1">
       <c r="A894" s="2" t="s">
         <v>1641</v>
       </c>
@@ -64491,7 +64492,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="895" spans="1:18">
+    <row r="895" spans="1:18" hidden="1">
       <c r="A895" s="2" t="s">
         <v>1643</v>
       </c>
@@ -64547,7 +64548,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="896" spans="1:18">
+    <row r="896" spans="1:18" hidden="1">
       <c r="A896" s="2" t="s">
         <v>1643</v>
       </c>
@@ -64603,7 +64604,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="897" spans="1:18">
+    <row r="897" spans="1:18" hidden="1">
       <c r="A897" s="2" t="s">
         <v>1645</v>
       </c>
@@ -64659,7 +64660,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="898" spans="1:18">
+    <row r="898" spans="1:18" hidden="1">
       <c r="A898" s="2" t="s">
         <v>1645</v>
       </c>
@@ -64715,7 +64716,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="899" spans="1:18">
+    <row r="899" spans="1:18" hidden="1">
       <c r="A899" s="2" t="s">
         <v>1647</v>
       </c>
@@ -64771,7 +64772,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="900" spans="1:18">
+    <row r="900" spans="1:18" hidden="1">
       <c r="A900" s="2" t="s">
         <v>1649</v>
       </c>
@@ -64827,7 +64828,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="901" spans="1:18">
+    <row r="901" spans="1:18" hidden="1">
       <c r="A901" s="2" t="s">
         <v>1651</v>
       </c>
@@ -64883,7 +64884,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="902" spans="1:18">
+    <row r="902" spans="1:18" hidden="1">
       <c r="A902" s="2" t="s">
         <v>1651</v>
       </c>
@@ -64939,7 +64940,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="903" spans="1:18">
+    <row r="903" spans="1:18" hidden="1">
       <c r="A903" s="2" t="s">
         <v>1653</v>
       </c>
@@ -64995,7 +64996,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="904" spans="1:18">
+    <row r="904" spans="1:18" hidden="1">
       <c r="A904" s="2" t="s">
         <v>1653</v>
       </c>
@@ -65051,7 +65052,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="905" spans="1:18">
+    <row r="905" spans="1:18" hidden="1">
       <c r="A905" s="2" t="s">
         <v>1655</v>
       </c>
@@ -65107,7 +65108,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="906" spans="1:18">
+    <row r="906" spans="1:18" hidden="1">
       <c r="A906" s="2" t="s">
         <v>1657</v>
       </c>
@@ -65163,7 +65164,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="907" spans="1:18">
+    <row r="907" spans="1:18" hidden="1">
       <c r="A907" s="2" t="s">
         <v>1659</v>
       </c>
@@ -65219,7 +65220,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="908" spans="1:18">
+    <row r="908" spans="1:18" hidden="1">
       <c r="A908" s="2" t="s">
         <v>1661</v>
       </c>
@@ -65275,7 +65276,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="909" spans="1:18">
+    <row r="909" spans="1:18" hidden="1">
       <c r="A909" s="2" t="s">
         <v>1663</v>
       </c>
@@ -65331,7 +65332,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="910" spans="1:18">
+    <row r="910" spans="1:18" hidden="1">
       <c r="A910" s="2" t="s">
         <v>1665</v>
       </c>
@@ -65387,7 +65388,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="911" spans="1:18">
+    <row r="911" spans="1:18" hidden="1">
       <c r="A911" s="2" t="s">
         <v>1667</v>
       </c>
@@ -65443,7 +65444,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="912" spans="1:18">
+    <row r="912" spans="1:18" hidden="1">
       <c r="A912" s="2" t="s">
         <v>1667</v>
       </c>
@@ -65499,7 +65500,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="913" spans="1:18">
+    <row r="913" spans="1:18" hidden="1">
       <c r="A913" s="2" t="s">
         <v>1669</v>
       </c>
@@ -65555,7 +65556,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="914" spans="1:18">
+    <row r="914" spans="1:18" hidden="1">
       <c r="A914" s="2" t="s">
         <v>1671</v>
       </c>
@@ -65611,7 +65612,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="915" spans="1:18">
+    <row r="915" spans="1:18" hidden="1">
       <c r="A915" s="2" t="s">
         <v>1673</v>
       </c>
@@ -65667,7 +65668,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="916" spans="1:18">
+    <row r="916" spans="1:18" hidden="1">
       <c r="A916" s="2" t="s">
         <v>1675</v>
       </c>
@@ -65723,7 +65724,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="917" spans="1:18">
+    <row r="917" spans="1:18" hidden="1">
       <c r="A917" s="2" t="s">
         <v>1677</v>
       </c>
@@ -65779,7 +65780,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="918" spans="1:18">
+    <row r="918" spans="1:18" hidden="1">
       <c r="A918" s="2" t="s">
         <v>1677</v>
       </c>
@@ -65835,7 +65836,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="919" spans="1:18">
+    <row r="919" spans="1:18" hidden="1">
       <c r="A919" s="2" t="s">
         <v>1679</v>
       </c>
@@ -65891,7 +65892,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="920" spans="1:18">
+    <row r="920" spans="1:18" hidden="1">
       <c r="A920" s="2" t="s">
         <v>1681</v>
       </c>
@@ -65947,7 +65948,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="921" spans="1:18">
+    <row r="921" spans="1:18" hidden="1">
       <c r="A921" s="2" t="s">
         <v>1683</v>
       </c>
@@ -66003,7 +66004,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="922" spans="1:18">
+    <row r="922" spans="1:18" hidden="1">
       <c r="A922" s="2" t="s">
         <v>1683</v>
       </c>
@@ -66059,7 +66060,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="923" spans="1:18">
+    <row r="923" spans="1:18" hidden="1">
       <c r="A923" s="2" t="s">
         <v>1685</v>
       </c>
@@ -66115,7 +66116,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="924" spans="1:18">
+    <row r="924" spans="1:18" hidden="1">
       <c r="A924" s="2" t="s">
         <v>1687</v>
       </c>
@@ -66171,7 +66172,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="925" spans="1:18">
+    <row r="925" spans="1:18" hidden="1">
       <c r="A925" s="2" t="s">
         <v>1689</v>
       </c>
@@ -66227,7 +66228,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="926" spans="1:18">
+    <row r="926" spans="1:18" hidden="1">
       <c r="A926" s="2" t="s">
         <v>1689</v>
       </c>
@@ -66283,7 +66284,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="927" spans="1:18">
+    <row r="927" spans="1:18" hidden="1">
       <c r="A927" s="2" t="s">
         <v>1691</v>
       </c>
@@ -66339,7 +66340,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="928" spans="1:18">
+    <row r="928" spans="1:18" hidden="1">
       <c r="A928" s="2" t="s">
         <v>1693</v>
       </c>
@@ -66395,7 +66396,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="929" spans="1:18">
+    <row r="929" spans="1:18" hidden="1">
       <c r="A929" s="2" t="s">
         <v>1695</v>
       </c>
@@ -66451,7 +66452,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="930" spans="1:18">
+    <row r="930" spans="1:18" hidden="1">
       <c r="A930" s="2" t="s">
         <v>1697</v>
       </c>
@@ -66507,7 +66508,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="931" spans="1:18">
+    <row r="931" spans="1:18" hidden="1">
       <c r="A931" s="2" t="s">
         <v>1699</v>
       </c>
@@ -66563,7 +66564,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="932" spans="1:18">
+    <row r="932" spans="1:18" hidden="1">
       <c r="A932" s="2" t="s">
         <v>1701</v>
       </c>
@@ -66619,7 +66620,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="933" spans="1:18">
+    <row r="933" spans="1:18" hidden="1">
       <c r="A933" s="2" t="s">
         <v>1703</v>
       </c>
@@ -66675,7 +66676,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="934" spans="1:18">
+    <row r="934" spans="1:18" hidden="1">
       <c r="A934" s="2" t="s">
         <v>1705</v>
       </c>
@@ -66731,7 +66732,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="935" spans="1:18">
+    <row r="935" spans="1:18" hidden="1">
       <c r="A935" s="2" t="s">
         <v>1707</v>
       </c>
@@ -66787,7 +66788,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="936" spans="1:18">
+    <row r="936" spans="1:18" hidden="1">
       <c r="A936" s="2" t="s">
         <v>1709</v>
       </c>
@@ -66843,7 +66844,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="937" spans="1:18">
+    <row r="937" spans="1:18" hidden="1">
       <c r="A937" s="2" t="s">
         <v>1711</v>
       </c>
@@ -66899,7 +66900,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="938" spans="1:18">
+    <row r="938" spans="1:18" hidden="1">
       <c r="A938" s="2" t="s">
         <v>1713</v>
       </c>
@@ -66955,7 +66956,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="939" spans="1:18">
+    <row r="939" spans="1:18" hidden="1">
       <c r="A939" s="2" t="s">
         <v>1715</v>
       </c>
@@ -67011,7 +67012,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="940" spans="1:18">
+    <row r="940" spans="1:18" hidden="1">
       <c r="A940" s="2" t="s">
         <v>1717</v>
       </c>
@@ -67123,7 +67124,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="942" spans="1:18">
+    <row r="942" spans="1:18" hidden="1">
       <c r="A942" s="2" t="s">
         <v>1721</v>
       </c>
@@ -67179,7 +67180,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="943" spans="1:18">
+    <row r="943" spans="1:18" hidden="1">
       <c r="A943" s="2" t="s">
         <v>1723</v>
       </c>
@@ -67235,7 +67236,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="944" spans="1:18">
+    <row r="944" spans="1:18" hidden="1">
       <c r="A944" s="2" t="s">
         <v>1725</v>
       </c>
@@ -67291,7 +67292,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="945" spans="1:18">
+    <row r="945" spans="1:18" hidden="1">
       <c r="A945" s="2" t="s">
         <v>1727</v>
       </c>
@@ -67347,7 +67348,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="946" spans="1:18">
+    <row r="946" spans="1:18" hidden="1">
       <c r="A946" s="2" t="s">
         <v>1727</v>
       </c>
@@ -67403,7 +67404,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="947" spans="1:18">
+    <row r="947" spans="1:18" hidden="1">
       <c r="A947" s="2" t="s">
         <v>1729</v>
       </c>
@@ -67459,7 +67460,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="948" spans="1:18">
+    <row r="948" spans="1:18" hidden="1">
       <c r="A948" s="2" t="s">
         <v>1731</v>
       </c>
@@ -67515,7 +67516,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="949" spans="1:18">
+    <row r="949" spans="1:18" hidden="1">
       <c r="A949" s="2" t="s">
         <v>1733</v>
       </c>
@@ -67571,7 +67572,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="950" spans="1:18">
+    <row r="950" spans="1:18" hidden="1">
       <c r="A950" s="2" t="s">
         <v>1733</v>
       </c>
@@ -67627,7 +67628,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="951" spans="1:18">
+    <row r="951" spans="1:18" hidden="1">
       <c r="A951" s="2" t="s">
         <v>1735</v>
       </c>
@@ -67683,7 +67684,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="952" spans="1:18">
+    <row r="952" spans="1:18" hidden="1">
       <c r="A952" s="2" t="s">
         <v>1737</v>
       </c>
@@ -67739,7 +67740,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="953" spans="1:18">
+    <row r="953" spans="1:18" hidden="1">
       <c r="A953" s="2" t="s">
         <v>1739</v>
       </c>
@@ -67795,7 +67796,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="954" spans="1:18">
+    <row r="954" spans="1:18" hidden="1">
       <c r="A954" s="2" t="s">
         <v>1741</v>
       </c>
@@ -67851,7 +67852,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="955" spans="1:18">
+    <row r="955" spans="1:18" hidden="1">
       <c r="A955" s="2" t="s">
         <v>1743</v>
       </c>
@@ -67907,7 +67908,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="956" spans="1:18">
+    <row r="956" spans="1:18" hidden="1">
       <c r="A956" s="2" t="s">
         <v>1745</v>
       </c>
@@ -67963,7 +67964,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="957" spans="1:18">
+    <row r="957" spans="1:18" hidden="1">
       <c r="A957" s="2" t="s">
         <v>1747</v>
       </c>
@@ -68019,7 +68020,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="958" spans="1:18">
+    <row r="958" spans="1:18" hidden="1">
       <c r="A958" s="2" t="s">
         <v>1747</v>
       </c>
@@ -68131,7 +68132,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="960" spans="1:18">
+    <row r="960" spans="1:18" hidden="1">
       <c r="A960" s="2" t="s">
         <v>1751</v>
       </c>
@@ -68243,7 +68244,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="962" spans="1:18">
+    <row r="962" spans="1:18" hidden="1">
       <c r="A962" s="2" t="s">
         <v>1755</v>
       </c>
@@ -68299,7 +68300,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="963" spans="1:18">
+    <row r="963" spans="1:18" hidden="1">
       <c r="A963" s="2" t="s">
         <v>1757</v>
       </c>
@@ -68355,7 +68356,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="964" spans="1:18">
+    <row r="964" spans="1:18" hidden="1">
       <c r="A964" s="2" t="s">
         <v>1759</v>
       </c>
@@ -68411,7 +68412,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="965" spans="1:18">
+    <row r="965" spans="1:18" hidden="1">
       <c r="A965" s="2" t="s">
         <v>1761</v>
       </c>
@@ -68467,7 +68468,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="966" spans="1:18">
+    <row r="966" spans="1:18" hidden="1">
       <c r="A966" s="2" t="s">
         <v>1763</v>
       </c>
@@ -68523,7 +68524,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="967" spans="1:18">
+    <row r="967" spans="1:18" hidden="1">
       <c r="A967" s="2" t="s">
         <v>1763</v>
       </c>
@@ -68579,7 +68580,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="968" spans="1:18">
+    <row r="968" spans="1:18" hidden="1">
       <c r="A968" s="2" t="s">
         <v>1765</v>
       </c>
@@ -68635,7 +68636,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="969" spans="1:18">
+    <row r="969" spans="1:18" hidden="1">
       <c r="A969" s="2" t="s">
         <v>1767</v>
       </c>
@@ -68691,7 +68692,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="970" spans="1:18">
+    <row r="970" spans="1:18" hidden="1">
       <c r="A970" s="2" t="s">
         <v>1769</v>
       </c>
@@ -68747,7 +68748,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="971" spans="1:18">
+    <row r="971" spans="1:18" hidden="1">
       <c r="A971" s="2" t="s">
         <v>1771</v>
       </c>
@@ -68803,7 +68804,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="972" spans="1:18">
+    <row r="972" spans="1:18" hidden="1">
       <c r="A972" s="2" t="s">
         <v>1773</v>
       </c>
@@ -68859,7 +68860,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="973" spans="1:18">
+    <row r="973" spans="1:18" hidden="1">
       <c r="A973" s="2" t="s">
         <v>1775</v>
       </c>
@@ -68915,7 +68916,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="974" spans="1:18">
+    <row r="974" spans="1:18" hidden="1">
       <c r="A974" s="2" t="s">
         <v>1777</v>
       </c>
@@ -68971,7 +68972,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="975" spans="1:18">
+    <row r="975" spans="1:18" hidden="1">
       <c r="A975" s="2" t="s">
         <v>1779</v>
       </c>
@@ -69027,7 +69028,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="976" spans="1:18">
+    <row r="976" spans="1:18" hidden="1">
       <c r="A976" s="2" t="s">
         <v>1781</v>
       </c>
@@ -69083,7 +69084,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="977" spans="1:18">
+    <row r="977" spans="1:18" hidden="1">
       <c r="A977" s="2" t="s">
         <v>1783</v>
       </c>
@@ -69139,7 +69140,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="978" spans="1:18">
+    <row r="978" spans="1:18" hidden="1">
       <c r="A978" s="2" t="s">
         <v>1785</v>
       </c>
@@ -69195,7 +69196,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="979" spans="1:18">
+    <row r="979" spans="1:18" hidden="1">
       <c r="A979" s="2" t="s">
         <v>1787</v>
       </c>
@@ -69251,7 +69252,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="980" spans="1:18">
+    <row r="980" spans="1:18" hidden="1">
       <c r="A980" s="2" t="s">
         <v>1789</v>
       </c>
@@ -69363,7 +69364,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="982" spans="1:18">
+    <row r="982" spans="1:18" hidden="1">
       <c r="A982" s="2" t="s">
         <v>1793</v>
       </c>
@@ -69419,7 +69420,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="983" spans="1:18">
+    <row r="983" spans="1:18" hidden="1">
       <c r="A983" s="2" t="s">
         <v>1795</v>
       </c>
@@ -69475,7 +69476,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="984" spans="1:18">
+    <row r="984" spans="1:18" hidden="1">
       <c r="A984" s="2" t="s">
         <v>1797</v>
       </c>
@@ -69531,7 +69532,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="985" spans="1:18">
+    <row r="985" spans="1:18" hidden="1">
       <c r="A985" s="2" t="s">
         <v>1799</v>
       </c>
@@ -69587,7 +69588,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="986" spans="1:18">
+    <row r="986" spans="1:18" hidden="1">
       <c r="A986" s="2" t="s">
         <v>1799</v>
       </c>
@@ -69643,7 +69644,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="987" spans="1:18">
+    <row r="987" spans="1:18" hidden="1">
       <c r="A987" s="2" t="s">
         <v>1801</v>
       </c>
@@ -69699,7 +69700,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="988" spans="1:18">
+    <row r="988" spans="1:18" hidden="1">
       <c r="A988" s="2" t="s">
         <v>1803</v>
       </c>
@@ -69755,7 +69756,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="989" spans="1:18">
+    <row r="989" spans="1:18" hidden="1">
       <c r="A989" s="2" t="s">
         <v>1805</v>
       </c>
@@ -69867,7 +69868,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="991" spans="1:18">
+    <row r="991" spans="1:18" hidden="1">
       <c r="A991" s="2" t="s">
         <v>1809</v>
       </c>
@@ -69923,7 +69924,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="992" spans="1:18">
+    <row r="992" spans="1:18" hidden="1">
       <c r="A992" s="2" t="s">
         <v>1809</v>
       </c>
@@ -69979,7 +69980,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="993" spans="1:18">
+    <row r="993" spans="1:18" hidden="1">
       <c r="A993" s="2" t="s">
         <v>1811</v>
       </c>
@@ -70035,7 +70036,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="994" spans="1:18">
+    <row r="994" spans="1:18" hidden="1">
       <c r="A994" s="2" t="s">
         <v>1813</v>
       </c>
@@ -70091,7 +70092,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="995" spans="1:18">
+    <row r="995" spans="1:18" hidden="1">
       <c r="A995" s="2" t="s">
         <v>1813</v>
       </c>
@@ -70147,7 +70148,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="996" spans="1:18">
+    <row r="996" spans="1:18" hidden="1">
       <c r="A996" s="2" t="s">
         <v>1815</v>
       </c>
@@ -70203,7 +70204,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="997" spans="1:18">
+    <row r="997" spans="1:18" hidden="1">
       <c r="A997" s="2" t="s">
         <v>1815</v>
       </c>
@@ -70259,7 +70260,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="998" spans="1:18">
+    <row r="998" spans="1:18" hidden="1">
       <c r="A998" s="2" t="s">
         <v>1817</v>
       </c>
@@ -70315,7 +70316,8 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="1000" spans="1:18" s="78" customFormat="1" ht="16">
+    <row r="999" spans="1:18" hidden="1"/>
+    <row r="1000" spans="1:18" s="78" customFormat="1" ht="16" hidden="1">
       <c r="F1000" s="79">
         <v>996</v>
       </c>
@@ -70365,7 +70367,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="Q1:Q1000" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="D1:D1000" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="产品名称(中文)"/>
+        <filter val="黑松露黑麦苏打饼干"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
